--- a/Experimenten5.xlsx
+++ b/Experimenten5.xlsx
@@ -8,19 +8,32 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://stichtingfontys-my.sharepoint.com/personal/582755_student_fontys_nl/Documents/Leerjaar 2/Periode 1/Operations Research 5/OR5/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_32BD246E17001417D5E0D4F0505ED87656CD5628" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8B4F17DF-5973-48F3-9919-F9819565D9C8}"/>
+  <xr:revisionPtr revIDLastSave="26" documentId="11_4419C470179018682943C3F0505ED87656CDA62E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5E4EB37B-4427-4221-8430-819D4794677D}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Random seeds" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029" calcCompleted="0"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
   <si>
     <t>t_max</t>
   </si>
@@ -53,6 +66,12 @@
   </si>
   <si>
     <t>Totale rekentijd (s)</t>
+  </si>
+  <si>
+    <t>Gemiddelde penalty</t>
+  </si>
+  <si>
+    <t>Afstand tot gemiddelde</t>
   </si>
 </sst>
 </file>
@@ -105,6 +124,1573 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-GB"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="nl-NL"/>
+              <a:t>Invloed van de random seed op de</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="nl-NL" baseline="0"/>
+              <a:t> totale penalty</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="nl-NL"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:v>Totale penalty</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="25400" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'Random seeds'!$E$2:$E$51</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="50"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>13</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>17</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>19</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>21</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>22</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>23</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>24</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>25</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>26</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>27</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>28</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>29</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>31</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>32</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>33</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>34</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>35</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>36</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>37</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>38</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>39</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>41</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>42</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>43</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>44</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>45</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>46</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>47</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>48</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>49</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>88</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'Random seeds'!$G$2:$G$51</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="50"/>
+                <c:pt idx="0">
+                  <c:v>156.0555555555556</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>370.58333333333343</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>460.08333333333331</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>371.61111111111109</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>267.25</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>294.52777777777783</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>445.41666666666657</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>520.7222222222224</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>288.05555555555537</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>519.27777777777783</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>329.5833333333332</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>420.27777777777771</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>206.33333333333329</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>252.1666666666668</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>282.80555555555549</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>292.8888888888888</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>389.77777777777811</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>253.25</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>298.49999999999989</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>379.49999999999989</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>560.58333333333337</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>316.55555555555571</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>419.6111111111112</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>282.33333333333343</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>353.99999999999989</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>288.38888888888891</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>294.50000000000011</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>394.88888888888869</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>458.91666666666652</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>393</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>426.44444444444451</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>144</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>359.97222222222229</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>471.50000000000011</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>504.24999999999977</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>305.94444444444417</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>273.83333333333331</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>501.94444444444468</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>267.94444444444429</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>398.58333333333331</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>337.00000000000011</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>267.25</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>460.13888888888903</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>388.02777777777749</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>389.72222222222229</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>169.6666666666666</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>360.86111111111092</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>213.6111111111112</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>249.44444444444451</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>433.83333333333343</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-16AF-4FCC-8A9D-4CE30B2AB55F}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:v>Gemiddelde penalty</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="25400" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent2"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'Random seeds'!$E$2:$E$51</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="50"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>13</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>17</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>19</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>21</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>22</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>23</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>24</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>25</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>26</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>27</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>28</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>29</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>31</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>32</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>33</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>34</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>35</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>36</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>37</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>38</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>39</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>41</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>42</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>43</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>44</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>45</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>46</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>47</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>48</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>49</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>88</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'Random seeds'!$N$47</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>349.70833333333326</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-16AF-4FCC-8A9D-4CE30B2AB55F}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="1410300847"/>
+        <c:axId val="713260047"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="1410300847"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="nl-NL" sz="1200"/>
+                  <a:t>Random</a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="nl-NL" sz="1200" baseline="0"/>
+                  <a:t> seed</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="nl-NL"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="nl-NL"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="713260047"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="713260047"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="nl-NL" sz="1200"/>
+                  <a:t>Totale penalty</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="nl-NL"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="nl-NL"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1410300847"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="nl-NL"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="nl-NL"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>247650</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>95250</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>29</xdr:col>
+      <xdr:colOff>95250</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Chart 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{35A03034-913D-0933-D1B8-F58A44C7A09A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -392,7 +1978,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K51"/>
+  <dimension ref="A1:N51"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6.42578125" bestFit="1" customWidth="1"/>
@@ -406,9 +1992,11 @@
     <col min="9" max="9" width="15.140625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="28.5703125" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="18.140625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="19.42578125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="22.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -442,1758 +2030,2169 @@
       <c r="K1" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>70000</v>
       </c>
       <c r="B2">
-        <v>0.99</v>
+        <v>0.95499999999999996</v>
       </c>
       <c r="C2">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="D2">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="E2">
         <v>1</v>
       </c>
       <c r="F2">
-        <v>2109.6111111111109</v>
+        <v>156.0555555555556</v>
       </c>
       <c r="G2">
-        <v>660.02777777777737</v>
+        <v>156.0555555555556</v>
       </c>
       <c r="H2">
-        <v>85.138888888888843</v>
+        <v>17.972222222222229</v>
       </c>
       <c r="I2">
-        <v>7.1987493000051472</v>
+        <v>4.2945706000027712</v>
       </c>
       <c r="J2">
-        <v>0.38867229998868419</v>
+        <v>3.4835400001611561E-2</v>
       </c>
       <c r="K2">
-        <v>7.5874215999938306</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+        <v>4.3294060000043828</v>
+      </c>
+      <c r="L2">
+        <f>AVERAGE($G$2:$G$51)</f>
+        <v>349.70833333333326</v>
+      </c>
+      <c r="M2">
+        <f>ABS(G2-$L$2)</f>
+        <v>193.65277777777766</v>
+      </c>
+      <c r="N2">
+        <f>$L$2</f>
+        <v>349.70833333333326</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>70000</v>
       </c>
       <c r="B3">
-        <v>0.99</v>
+        <v>0.95499999999999996</v>
       </c>
       <c r="C3">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="D3">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="E3">
         <v>2</v>
       </c>
       <c r="F3">
-        <v>2135.9444444444448</v>
+        <v>370.58333333333343</v>
       </c>
       <c r="G3">
-        <v>1331.6388888888889</v>
+        <v>370.58333333333343</v>
       </c>
       <c r="H3">
-        <v>163.25</v>
+        <v>55.138888888888893</v>
       </c>
       <c r="I3">
-        <v>5.8632376000023214</v>
+        <v>4.6066441000002669</v>
       </c>
       <c r="J3">
-        <v>0.2430941000056919</v>
+        <v>2.6499399988097139E-2</v>
       </c>
       <c r="K3">
-        <v>6.1063317000080133</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+        <v>4.6331434999883641</v>
+      </c>
+      <c r="M3">
+        <f t="shared" ref="M3:M51" si="0">ABS(G3-$L$2)</f>
+        <v>20.875000000000171</v>
+      </c>
+      <c r="N3">
+        <f t="shared" ref="N3:N51" si="1">$L$2</f>
+        <v>349.70833333333326</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>70000</v>
       </c>
       <c r="B4">
-        <v>0.99</v>
+        <v>0.95499999999999996</v>
       </c>
       <c r="C4">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="D4">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="E4">
         <v>3</v>
       </c>
       <c r="F4">
-        <v>1837.194444444445</v>
+        <v>483.33333333333331</v>
       </c>
       <c r="G4">
-        <v>629.19444444444434</v>
+        <v>460.08333333333331</v>
       </c>
       <c r="H4">
-        <v>78.305555555555543</v>
+        <v>67.249999999999986</v>
       </c>
       <c r="I4">
-        <v>5.8186602000059793</v>
+        <v>4.5204039999953238</v>
       </c>
       <c r="J4">
-        <v>0.30929079999623349</v>
+        <v>4.8616200001561083E-2</v>
       </c>
       <c r="K4">
-        <v>6.1279510000022128</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+        <v>4.5690201999968849</v>
+      </c>
+      <c r="M4">
+        <f t="shared" si="0"/>
+        <v>110.37500000000006</v>
+      </c>
+      <c r="N4">
+        <f t="shared" si="1"/>
+        <v>349.70833333333326</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>70000</v>
       </c>
       <c r="B5">
-        <v>0.99</v>
+        <v>0.95499999999999996</v>
       </c>
       <c r="C5">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="D5">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="E5">
         <v>4</v>
       </c>
       <c r="F5">
-        <v>2079.1388888888891</v>
+        <v>371.61111111111109</v>
       </c>
       <c r="G5">
-        <v>573.52777777777783</v>
+        <v>371.61111111111109</v>
       </c>
       <c r="H5">
-        <v>83.6388888888889</v>
+        <v>56.333333333333343</v>
       </c>
       <c r="I5">
-        <v>5.8566919000004418</v>
+        <v>4.4489886000083061</v>
       </c>
       <c r="J5">
-        <v>0.38327279999793967</v>
+        <v>2.6855700009036809E-2</v>
       </c>
       <c r="K5">
-        <v>6.2399646999983824</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+        <v>4.4758443000173429</v>
+      </c>
+      <c r="M5">
+        <f t="shared" si="0"/>
+        <v>21.902777777777828</v>
+      </c>
+      <c r="N5">
+        <f t="shared" si="1"/>
+        <v>349.70833333333326</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>70000</v>
       </c>
       <c r="B6">
-        <v>0.99</v>
+        <v>0.95499999999999996</v>
       </c>
       <c r="C6">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="D6">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="E6">
         <v>5</v>
       </c>
       <c r="F6">
-        <v>2255.6944444444448</v>
+        <v>267.25</v>
       </c>
       <c r="G6">
-        <v>586.47222222222217</v>
+        <v>267.25</v>
       </c>
       <c r="H6">
-        <v>88.388888888888886</v>
+        <v>42.416666666666657</v>
       </c>
       <c r="I6">
-        <v>5.8674118000053568</v>
+        <v>4.4760458999953698</v>
       </c>
       <c r="J6">
-        <v>0.499396599989268</v>
+        <v>2.5460699995164759E-2</v>
       </c>
       <c r="K6">
-        <v>6.3668083999946248</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+        <v>4.5015065999905346</v>
+      </c>
+      <c r="M6">
+        <f t="shared" si="0"/>
+        <v>82.458333333333258</v>
+      </c>
+      <c r="N6">
+        <f t="shared" si="1"/>
+        <v>349.70833333333326</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>70000</v>
       </c>
       <c r="B7">
-        <v>0.99</v>
+        <v>0.95499999999999996</v>
       </c>
       <c r="C7">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="D7">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="E7">
         <v>6</v>
       </c>
       <c r="F7">
-        <v>2171.833333333333</v>
+        <v>294.52777777777783</v>
       </c>
       <c r="G7">
-        <v>848.83333333333337</v>
+        <v>294.52777777777783</v>
       </c>
       <c r="H7">
-        <v>111.4722222222222</v>
+        <v>43.694444444444443</v>
       </c>
       <c r="I7">
-        <v>5.9137117999925977</v>
+        <v>4.5316634000046179</v>
       </c>
       <c r="J7">
-        <v>0.38207190000684932</v>
+        <v>2.4096699999063279E-2</v>
       </c>
       <c r="K7">
-        <v>6.295783699999447</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+        <v>4.5557601000036811</v>
+      </c>
+      <c r="M7">
+        <f t="shared" si="0"/>
+        <v>55.180555555555429</v>
+      </c>
+      <c r="N7">
+        <f t="shared" si="1"/>
+        <v>349.70833333333326</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>70000</v>
       </c>
       <c r="B8">
-        <v>0.99</v>
+        <v>0.95499999999999996</v>
       </c>
       <c r="C8">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="D8">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="E8">
         <v>7</v>
       </c>
       <c r="F8">
-        <v>2140.9722222222231</v>
+        <v>445.41666666666657</v>
       </c>
       <c r="G8">
-        <v>1101.0277777777769</v>
+        <v>445.41666666666657</v>
       </c>
       <c r="H8">
-        <v>114.75</v>
+        <v>59.583333333333329</v>
       </c>
       <c r="I8">
-        <v>5.9129920999985188</v>
+        <v>4.1914077999972514</v>
       </c>
       <c r="J8">
-        <v>0.2926444999902742</v>
+        <v>3.5960499997599982E-2</v>
       </c>
       <c r="K8">
-        <v>6.205636599988793</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+        <v>4.2273682999948514</v>
+      </c>
+      <c r="M8">
+        <f t="shared" si="0"/>
+        <v>95.708333333333314</v>
+      </c>
+      <c r="N8">
+        <f t="shared" si="1"/>
+        <v>349.70833333333326</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>70000</v>
       </c>
       <c r="B9">
-        <v>0.99</v>
+        <v>0.95499999999999996</v>
       </c>
       <c r="C9">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="D9">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="E9">
         <v>8</v>
       </c>
       <c r="F9">
-        <v>2149.6666666666661</v>
+        <v>520.7222222222224</v>
       </c>
       <c r="G9">
-        <v>643.77777777777737</v>
+        <v>520.7222222222224</v>
       </c>
       <c r="H9">
-        <v>87.888888888888857</v>
+        <v>70.083333333333343</v>
       </c>
       <c r="I9">
-        <v>5.9635417999961646</v>
+        <v>4.6589655999996467</v>
       </c>
       <c r="J9">
-        <v>0.36486349999904633</v>
+        <v>2.707709999231156E-2</v>
       </c>
       <c r="K9">
-        <v>6.328405299995211</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+        <v>4.6860426999919582</v>
+      </c>
+      <c r="M9">
+        <f t="shared" si="0"/>
+        <v>171.01388888888914</v>
+      </c>
+      <c r="N9">
+        <f t="shared" si="1"/>
+        <v>349.70833333333326</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>70000</v>
       </c>
       <c r="B10">
-        <v>0.99</v>
+        <v>0.95499999999999996</v>
       </c>
       <c r="C10">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="D10">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="E10">
         <v>9</v>
       </c>
       <c r="F10">
-        <v>2207.8611111111109</v>
+        <v>288.05555555555537</v>
       </c>
       <c r="G10">
-        <v>1206.583333333333</v>
+        <v>288.05555555555537</v>
       </c>
       <c r="H10">
-        <v>142.99999999999989</v>
+        <v>42.694444444444443</v>
       </c>
       <c r="I10">
-        <v>5.8278903999889744</v>
+        <v>4.5848924000019906</v>
       </c>
       <c r="J10">
-        <v>0.45777430001180619</v>
+        <v>2.5847099997918122E-2</v>
       </c>
       <c r="K10">
-        <v>6.2856647000007797</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+        <v>4.6107394999999087</v>
+      </c>
+      <c r="M10">
+        <f t="shared" si="0"/>
+        <v>61.652777777777885</v>
+      </c>
+      <c r="N10">
+        <f t="shared" si="1"/>
+        <v>349.70833333333326</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>70000</v>
       </c>
       <c r="B11">
-        <v>0.99</v>
+        <v>0.95499999999999996</v>
       </c>
       <c r="C11">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="D11">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="E11">
         <v>10</v>
       </c>
       <c r="F11">
-        <v>2209.333333333333</v>
+        <v>519.27777777777783</v>
       </c>
       <c r="G11">
-        <v>905.33333333333348</v>
+        <v>519.27777777777783</v>
       </c>
       <c r="H11">
-        <v>113.7222222222222</v>
+        <v>62.916666666666671</v>
       </c>
       <c r="I11">
-        <v>6.0200703000009526</v>
+        <v>4.442677700004424</v>
       </c>
       <c r="J11">
-        <v>0.43027920000895392</v>
+        <v>2.6426300013554279E-2</v>
       </c>
       <c r="K11">
-        <v>6.4503495000099056</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+        <v>4.4691040000179783</v>
+      </c>
+      <c r="M11">
+        <f t="shared" si="0"/>
+        <v>169.56944444444457</v>
+      </c>
+      <c r="N11">
+        <f t="shared" si="1"/>
+        <v>349.70833333333326</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>70000</v>
       </c>
       <c r="B12">
-        <v>0.99</v>
+        <v>0.95499999999999996</v>
       </c>
       <c r="C12">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="D12">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="E12">
         <v>11</v>
       </c>
       <c r="F12">
-        <v>2156.1388888888891</v>
+        <v>329.5833333333332</v>
       </c>
       <c r="G12">
-        <v>1141.6944444444439</v>
+        <v>329.5833333333332</v>
       </c>
       <c r="H12">
-        <v>151.69444444444451</v>
+        <v>49.416666666666643</v>
       </c>
       <c r="I12">
-        <v>5.8407997999893269</v>
+        <v>4.6914169000083348</v>
       </c>
       <c r="J12">
-        <v>0.4003592000080971</v>
+        <v>2.5309799995739009E-2</v>
       </c>
       <c r="K12">
-        <v>6.241158999997424</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+        <v>4.7167267000040738</v>
+      </c>
+      <c r="M12">
+        <f t="shared" si="0"/>
+        <v>20.125000000000057</v>
+      </c>
+      <c r="N12">
+        <f t="shared" si="1"/>
+        <v>349.70833333333326</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>70000</v>
       </c>
       <c r="B13">
-        <v>0.99</v>
+        <v>0.95499999999999996</v>
       </c>
       <c r="C13">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="D13">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="E13">
         <v>12</v>
       </c>
       <c r="F13">
-        <v>2167.0277777777769</v>
+        <v>420.27777777777771</v>
       </c>
       <c r="G13">
-        <v>547.91666666666674</v>
+        <v>420.27777777777771</v>
       </c>
       <c r="H13">
-        <v>58.416666666666671</v>
+        <v>47.583333333333329</v>
       </c>
       <c r="I13">
-        <v>5.8762216000031913</v>
+        <v>4.6121975999994902</v>
       </c>
       <c r="J13">
-        <v>0.61744319999706931</v>
+        <v>2.5985000000218861E-2</v>
       </c>
       <c r="K13">
-        <v>6.4936648000002606</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+        <v>4.6381825999997091</v>
+      </c>
+      <c r="M13">
+        <f t="shared" si="0"/>
+        <v>70.569444444444457</v>
+      </c>
+      <c r="N13">
+        <f t="shared" si="1"/>
+        <v>349.70833333333326</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>70000</v>
       </c>
       <c r="B14">
-        <v>0.99</v>
+        <v>0.95499999999999996</v>
       </c>
       <c r="C14">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="D14">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="E14">
         <v>13</v>
       </c>
       <c r="F14">
-        <v>2216.1666666666661</v>
+        <v>224.5</v>
       </c>
       <c r="G14">
-        <v>807.22222222222194</v>
+        <v>206.33333333333329</v>
       </c>
       <c r="H14">
-        <v>108.9166666666666</v>
+        <v>29.055555555555561</v>
       </c>
       <c r="I14">
-        <v>5.9002398999873549</v>
+        <v>4.6470414999930654</v>
       </c>
       <c r="J14">
-        <v>0.3585834999976214</v>
+        <v>7.4611599993659183E-2</v>
       </c>
       <c r="K14">
-        <v>6.2588233999849763</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+        <v>4.7216530999867254</v>
+      </c>
+      <c r="M14">
+        <f t="shared" si="0"/>
+        <v>143.37499999999997</v>
+      </c>
+      <c r="N14">
+        <f t="shared" si="1"/>
+        <v>349.70833333333326</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>70000</v>
       </c>
       <c r="B15">
-        <v>0.99</v>
+        <v>0.95499999999999996</v>
       </c>
       <c r="C15">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="D15">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="E15">
         <v>14</v>
       </c>
       <c r="F15">
-        <v>2230.7222222222222</v>
+        <v>255.6666666666668</v>
       </c>
       <c r="G15">
-        <v>444.05555555555571</v>
+        <v>252.1666666666668</v>
       </c>
       <c r="H15">
-        <v>49.527777777777793</v>
+        <v>40.000000000000007</v>
       </c>
       <c r="I15">
-        <v>5.8435226000001421</v>
+        <v>4.4126542000012714</v>
       </c>
       <c r="J15">
-        <v>0.53269039999577217</v>
+        <v>4.8726399996667169E-2</v>
       </c>
       <c r="K15">
-        <v>6.3762129999959143</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+        <v>4.4613805999979377</v>
+      </c>
+      <c r="M15">
+        <f t="shared" si="0"/>
+        <v>97.541666666666458</v>
+      </c>
+      <c r="N15">
+        <f t="shared" si="1"/>
+        <v>349.70833333333326</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>70000</v>
       </c>
       <c r="B16">
-        <v>0.99</v>
+        <v>0.95499999999999996</v>
       </c>
       <c r="C16">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="D16">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="E16">
         <v>15</v>
       </c>
       <c r="F16">
-        <v>2338.3333333333339</v>
+        <v>411.52777777777783</v>
       </c>
       <c r="G16">
-        <v>1168.9722222222231</v>
+        <v>282.80555555555549</v>
       </c>
       <c r="H16">
-        <v>152.3333333333334</v>
+        <v>34.805555555555557</v>
       </c>
       <c r="I16">
-        <v>5.9192158999940148</v>
+        <v>4.670396499990602</v>
       </c>
       <c r="J16">
-        <v>0.3514469000074314</v>
+        <v>9.1184300006716512E-2</v>
       </c>
       <c r="K16">
-        <v>6.2706628000014462</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
+        <v>4.7615807999973194</v>
+      </c>
+      <c r="M16">
+        <f t="shared" si="0"/>
+        <v>66.902777777777771</v>
+      </c>
+      <c r="N16">
+        <f t="shared" si="1"/>
+        <v>349.70833333333326</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>70000</v>
       </c>
       <c r="B17">
-        <v>0.99</v>
+        <v>0.95499999999999996</v>
       </c>
       <c r="C17">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="D17">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="E17">
         <v>16</v>
       </c>
       <c r="F17">
-        <v>2309</v>
+        <v>292.8888888888888</v>
       </c>
       <c r="G17">
-        <v>362.52777777777783</v>
+        <v>292.8888888888888</v>
       </c>
       <c r="H17">
-        <v>35.444444444444443</v>
+        <v>33.6111111111111</v>
       </c>
       <c r="I17">
-        <v>5.9518784999963827</v>
+        <v>4.7255049999948824</v>
       </c>
       <c r="J17">
-        <v>0.65268299999297597</v>
+        <v>2.6741599998786111E-2</v>
       </c>
       <c r="K17">
-        <v>6.6045614999893587</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
+        <v>4.7522465999936676</v>
+      </c>
+      <c r="M17">
+        <f t="shared" si="0"/>
+        <v>56.819444444444457</v>
+      </c>
+      <c r="N17">
+        <f t="shared" si="1"/>
+        <v>349.70833333333326</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>70000</v>
       </c>
       <c r="B18">
-        <v>0.99</v>
+        <v>0.95499999999999996</v>
       </c>
       <c r="C18">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="D18">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="E18">
         <v>17</v>
       </c>
       <c r="F18">
-        <v>1971.111111111112</v>
+        <v>389.77777777777811</v>
       </c>
       <c r="G18">
-        <v>658.77777777777783</v>
+        <v>389.77777777777811</v>
       </c>
       <c r="H18">
-        <v>86.527777777777786</v>
+        <v>57.750000000000028</v>
       </c>
       <c r="I18">
-        <v>5.997253699999419</v>
+        <v>4.5051876999932574</v>
       </c>
       <c r="J18">
-        <v>0.41792420001002029</v>
+        <v>2.740419999463484E-2</v>
       </c>
       <c r="K18">
-        <v>6.4151779000094393</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
+        <v>4.5325918999878922</v>
+      </c>
+      <c r="M18">
+        <f t="shared" si="0"/>
+        <v>40.069444444444855</v>
+      </c>
+      <c r="N18">
+        <f t="shared" si="1"/>
+        <v>349.70833333333326</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>70000</v>
       </c>
       <c r="B19">
-        <v>0.99</v>
+        <v>0.95499999999999996</v>
       </c>
       <c r="C19">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="D19">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="E19">
         <v>18</v>
       </c>
       <c r="F19">
-        <v>2365.6944444444439</v>
+        <v>253.25</v>
       </c>
       <c r="G19">
-        <v>747.88888888888914</v>
+        <v>253.25</v>
       </c>
       <c r="H19">
-        <v>105.8333333333334</v>
+        <v>39.416666666666657</v>
       </c>
       <c r="I19">
-        <v>5.8868724000058137</v>
+        <v>4.521092499999213</v>
       </c>
       <c r="J19">
-        <v>0.57996899999852758</v>
+        <v>2.4690299993380901E-2</v>
       </c>
       <c r="K19">
-        <v>6.4668414000043413</v>
-      </c>
-    </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
+        <v>4.5457827999925939</v>
+      </c>
+      <c r="M19">
+        <f t="shared" si="0"/>
+        <v>96.458333333333258</v>
+      </c>
+      <c r="N19">
+        <f t="shared" si="1"/>
+        <v>349.70833333333326</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>70000</v>
       </c>
       <c r="B20">
-        <v>0.99</v>
+        <v>0.95499999999999996</v>
       </c>
       <c r="C20">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="D20">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="E20">
         <v>19</v>
       </c>
       <c r="F20">
-        <v>2056</v>
+        <v>298.49999999999989</v>
       </c>
       <c r="G20">
-        <v>670.55555555555554</v>
+        <v>298.49999999999989</v>
       </c>
       <c r="H20">
-        <v>96.194444444444443</v>
+        <v>43.41666666666665</v>
       </c>
       <c r="I20">
-        <v>5.9498553999874284</v>
+        <v>4.4804460999876028</v>
       </c>
       <c r="J20">
-        <v>0.41751890000887221</v>
+        <v>2.4080200004391369E-2</v>
       </c>
       <c r="K20">
-        <v>6.3673742999962997</v>
-      </c>
-    </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
+        <v>4.5045262999919942</v>
+      </c>
+      <c r="M20">
+        <f t="shared" si="0"/>
+        <v>51.208333333333371</v>
+      </c>
+      <c r="N20">
+        <f t="shared" si="1"/>
+        <v>349.70833333333326</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>70000</v>
       </c>
       <c r="B21">
-        <v>0.99</v>
+        <v>0.95499999999999996</v>
       </c>
       <c r="C21">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="D21">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="E21">
         <v>20</v>
       </c>
       <c r="F21">
-        <v>1785.833333333333</v>
+        <v>379.49999999999989</v>
       </c>
       <c r="G21">
-        <v>776.7222222222224</v>
+        <v>379.49999999999989</v>
       </c>
       <c r="H21">
-        <v>86.833333333333343</v>
+        <v>54.305555555555543</v>
       </c>
       <c r="I21">
-        <v>5.8185154999955557</v>
+        <v>4.5414391999947838</v>
       </c>
       <c r="J21">
-        <v>0.3469036999886157</v>
+        <v>2.7172000001883131E-2</v>
       </c>
       <c r="K21">
-        <v>6.1654191999841714</v>
-      </c>
-    </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
+        <v>4.568611199996667</v>
+      </c>
+      <c r="M21">
+        <f t="shared" si="0"/>
+        <v>29.791666666666629</v>
+      </c>
+      <c r="N21">
+        <f t="shared" si="1"/>
+        <v>349.70833333333326</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>70000</v>
       </c>
       <c r="B22">
-        <v>0.99</v>
+        <v>0.95499999999999996</v>
       </c>
       <c r="C22">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="D22">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="E22">
         <v>21</v>
       </c>
       <c r="F22">
-        <v>2105.416666666667</v>
+        <v>560.58333333333337</v>
       </c>
       <c r="G22">
-        <v>1561.333333333333</v>
+        <v>560.58333333333337</v>
       </c>
       <c r="H22">
-        <v>156.24999999999989</v>
+        <v>75.666666666666671</v>
       </c>
       <c r="I22">
-        <v>5.8900484000041624</v>
+        <v>4.6203573999955552</v>
       </c>
       <c r="J22">
-        <v>0.17044549999991429</v>
+        <v>2.602039999328554E-2</v>
       </c>
       <c r="K22">
-        <v>6.0604939000040758</v>
-      </c>
-    </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
+        <v>4.6463777999888407</v>
+      </c>
+      <c r="M22">
+        <f t="shared" si="0"/>
+        <v>210.87500000000011</v>
+      </c>
+      <c r="N22">
+        <f t="shared" si="1"/>
+        <v>349.70833333333326</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>70000</v>
       </c>
       <c r="B23">
-        <v>0.99</v>
+        <v>0.95499999999999996</v>
       </c>
       <c r="C23">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="D23">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="E23">
         <v>22</v>
       </c>
       <c r="F23">
-        <v>1994.444444444445</v>
+        <v>316.55555555555571</v>
       </c>
       <c r="G23">
-        <v>635.2777777777776</v>
+        <v>316.55555555555571</v>
       </c>
       <c r="H23">
-        <v>81.999999999999972</v>
+        <v>46.722222222222229</v>
       </c>
       <c r="I23">
-        <v>5.9524453000049107</v>
+        <v>4.4373579999955837</v>
       </c>
       <c r="J23">
-        <v>0.41126619999704422</v>
+        <v>2.4686500008101579E-2</v>
       </c>
       <c r="K23">
-        <v>6.3637115000019548</v>
-      </c>
-    </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
+        <v>4.4620445000036852</v>
+      </c>
+      <c r="M23">
+        <f t="shared" si="0"/>
+        <v>33.152777777777544</v>
+      </c>
+      <c r="N23">
+        <f t="shared" si="1"/>
+        <v>349.70833333333326</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>70000</v>
       </c>
       <c r="B24">
-        <v>0.99</v>
+        <v>0.95499999999999996</v>
       </c>
       <c r="C24">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="D24">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="E24">
         <v>23</v>
       </c>
       <c r="F24">
-        <v>1984.1944444444439</v>
+        <v>441.6111111111112</v>
       </c>
       <c r="G24">
-        <v>1057.166666666667</v>
+        <v>419.6111111111112</v>
       </c>
       <c r="H24">
-        <v>135.41666666666671</v>
+        <v>58.000000000000007</v>
       </c>
       <c r="I24">
-        <v>5.8392763000010746</v>
+        <v>4.5276949000108289</v>
       </c>
       <c r="J24">
-        <v>0.38247929999488411</v>
+        <v>4.9588200010475703E-2</v>
       </c>
       <c r="K24">
-        <v>6.2217555999959586</v>
-      </c>
-    </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
+        <v>4.5772831000213046</v>
+      </c>
+      <c r="M24">
+        <f t="shared" si="0"/>
+        <v>69.902777777777942</v>
+      </c>
+      <c r="N24">
+        <f t="shared" si="1"/>
+        <v>349.70833333333326</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>70000</v>
       </c>
       <c r="B25">
-        <v>0.99</v>
+        <v>0.95499999999999996</v>
       </c>
       <c r="C25">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="D25">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="E25">
         <v>24</v>
       </c>
       <c r="F25">
-        <v>2445.5277777777778</v>
+        <v>282.33333333333343</v>
       </c>
       <c r="G25">
-        <v>875.94444444444423</v>
+        <v>282.33333333333343</v>
       </c>
       <c r="H25">
-        <v>121.6944444444444</v>
+        <v>31.250000000000011</v>
       </c>
       <c r="I25">
-        <v>5.961981200001901</v>
+        <v>4.5951457000046503</v>
       </c>
       <c r="J25">
-        <v>0.53846830000111368</v>
+        <v>2.4164899994502779E-2</v>
       </c>
       <c r="K25">
-        <v>6.5004495000030147</v>
-      </c>
-    </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
+        <v>4.6193105999991531</v>
+      </c>
+      <c r="M25">
+        <f t="shared" si="0"/>
+        <v>67.374999999999829</v>
+      </c>
+      <c r="N25">
+        <f t="shared" si="1"/>
+        <v>349.70833333333326</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>70000</v>
       </c>
       <c r="B26">
-        <v>0.99</v>
+        <v>0.95499999999999996</v>
       </c>
       <c r="C26">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="D26">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="E26">
         <v>25</v>
       </c>
       <c r="F26">
-        <v>2046.583333333333</v>
+        <v>365.99999999999989</v>
       </c>
       <c r="G26">
-        <v>474.83333333333348</v>
+        <v>353.99999999999989</v>
       </c>
       <c r="H26">
-        <v>70.000000000000014</v>
+        <v>50.583333333333321</v>
       </c>
       <c r="I26">
-        <v>6.0676581000006991</v>
+        <v>4.553966199993738</v>
       </c>
       <c r="J26">
-        <v>0.72898980000172742</v>
+        <v>4.7483100002864383E-2</v>
       </c>
       <c r="K26">
-        <v>6.7966479000024256</v>
-      </c>
-    </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
+        <v>4.6014492999966023</v>
+      </c>
+      <c r="M26">
+        <f t="shared" si="0"/>
+        <v>4.2916666666666288</v>
+      </c>
+      <c r="N26">
+        <f t="shared" si="1"/>
+        <v>349.70833333333326</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>70000</v>
       </c>
       <c r="B27">
-        <v>0.99</v>
+        <v>0.95499999999999996</v>
       </c>
       <c r="C27">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="D27">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="E27">
         <v>26</v>
       </c>
       <c r="F27">
-        <v>2098.2222222222231</v>
+        <v>288.38888888888891</v>
       </c>
       <c r="G27">
-        <v>999.8888888888888</v>
+        <v>288.38888888888891</v>
       </c>
       <c r="H27">
-        <v>103.2222222222222</v>
+        <v>42.527777777777779</v>
       </c>
       <c r="I27">
-        <v>5.9079497999919113</v>
+        <v>4.4120253000000957</v>
       </c>
       <c r="J27">
-        <v>0.30974679999053478</v>
+        <v>2.447530000063125E-2</v>
       </c>
       <c r="K27">
-        <v>6.2176965999824461</v>
-      </c>
-    </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
+        <v>4.436500600000727</v>
+      </c>
+      <c r="M27">
+        <f t="shared" si="0"/>
+        <v>61.319444444444343</v>
+      </c>
+      <c r="N27">
+        <f t="shared" si="1"/>
+        <v>349.70833333333326</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>70000</v>
       </c>
       <c r="B28">
-        <v>0.99</v>
+        <v>0.95499999999999996</v>
       </c>
       <c r="C28">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="D28">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="E28">
         <v>27</v>
       </c>
       <c r="F28">
-        <v>2044.416666666667</v>
+        <v>294.50000000000011</v>
       </c>
       <c r="G28">
-        <v>793.9722222222224</v>
+        <v>294.50000000000011</v>
       </c>
       <c r="H28">
-        <v>101.4166666666667</v>
+        <v>42.888888888888893</v>
       </c>
       <c r="I28">
-        <v>5.9190013000043109</v>
+        <v>4.704649999999674</v>
       </c>
       <c r="J28">
-        <v>0.32334910001372918</v>
+        <v>3.6172899999655783E-2</v>
       </c>
       <c r="K28">
-        <v>6.2423504000180401</v>
-      </c>
-    </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
+        <v>4.7408228999993298</v>
+      </c>
+      <c r="M28">
+        <f t="shared" si="0"/>
+        <v>55.208333333333144</v>
+      </c>
+      <c r="N28">
+        <f t="shared" si="1"/>
+        <v>349.70833333333326</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>70000</v>
       </c>
       <c r="B29">
-        <v>0.99</v>
+        <v>0.95499999999999996</v>
       </c>
       <c r="C29">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="D29">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="E29">
         <v>28</v>
       </c>
       <c r="F29">
-        <v>1969.3055555555561</v>
+        <v>394.88888888888869</v>
       </c>
       <c r="G29">
-        <v>1196.25</v>
+        <v>394.88888888888869</v>
       </c>
       <c r="H29">
-        <v>158.41666666666671</v>
+        <v>58.166666666666643</v>
       </c>
       <c r="I29">
-        <v>5.944156000012299</v>
+        <v>4.7666188999864971</v>
       </c>
       <c r="J29">
-        <v>0.29110790000413539</v>
+        <v>2.6740700006484989E-2</v>
       </c>
       <c r="K29">
-        <v>6.2352639000164336</v>
-      </c>
-    </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
+        <v>4.7933595999929821</v>
+      </c>
+      <c r="M29">
+        <f t="shared" si="0"/>
+        <v>45.180555555555429</v>
+      </c>
+      <c r="N29">
+        <f t="shared" si="1"/>
+        <v>349.70833333333326</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>70000</v>
       </c>
       <c r="B30">
-        <v>0.99</v>
+        <v>0.95499999999999996</v>
       </c>
       <c r="C30">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="D30">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="E30">
         <v>29</v>
       </c>
       <c r="F30">
-        <v>2295.6111111111109</v>
+        <v>458.91666666666652</v>
       </c>
       <c r="G30">
-        <v>1029.861111111112</v>
+        <v>458.91666666666652</v>
       </c>
       <c r="H30">
-        <v>115.9722222222223</v>
+        <v>59.999999999999972</v>
       </c>
       <c r="I30">
-        <v>5.8975378000031924</v>
+        <v>4.5738898000126937</v>
       </c>
       <c r="J30">
-        <v>0.31019699999887962</v>
+        <v>2.6802000007592142E-2</v>
       </c>
       <c r="K30">
-        <v>6.207734800002072</v>
-      </c>
-    </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
+        <v>4.6006918000202859</v>
+      </c>
+      <c r="M30">
+        <f t="shared" si="0"/>
+        <v>109.20833333333326</v>
+      </c>
+      <c r="N30">
+        <f t="shared" si="1"/>
+        <v>349.70833333333326</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>70000</v>
       </c>
       <c r="B31">
-        <v>0.99</v>
+        <v>0.95499999999999996</v>
       </c>
       <c r="C31">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="D31">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="E31">
         <v>30</v>
       </c>
       <c r="F31">
-        <v>2138.166666666667</v>
+        <v>393</v>
       </c>
       <c r="G31">
-        <v>371.33333333333388</v>
+        <v>393</v>
       </c>
       <c r="H31">
-        <v>46.000000000000057</v>
+        <v>54.916666666666671</v>
       </c>
       <c r="I31">
-        <v>5.9844748000032268</v>
+        <v>4.5056306000042241</v>
       </c>
       <c r="J31">
-        <v>0.50737639999715611</v>
+        <v>2.8951399988727641E-2</v>
       </c>
       <c r="K31">
-        <v>6.491851200000383</v>
-      </c>
-    </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
+        <v>4.5345819999929518</v>
+      </c>
+      <c r="M31">
+        <f t="shared" si="0"/>
+        <v>43.291666666666742</v>
+      </c>
+      <c r="N31">
+        <f t="shared" si="1"/>
+        <v>349.70833333333326</v>
+      </c>
+    </row>
+    <row r="32" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>70000</v>
       </c>
       <c r="B32">
-        <v>0.99</v>
+        <v>0.95499999999999996</v>
       </c>
       <c r="C32">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="D32">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="E32">
         <v>31</v>
       </c>
       <c r="F32">
-        <v>2094.0555555555561</v>
+        <v>426.44444444444451</v>
       </c>
       <c r="G32">
-        <v>461.75</v>
+        <v>426.44444444444451</v>
       </c>
       <c r="H32">
-        <v>76</v>
+        <v>58.638888888888893</v>
       </c>
       <c r="I32">
-        <v>5.9596069999970496</v>
+        <v>4.5530281999963336</v>
       </c>
       <c r="J32">
-        <v>0.39734559999487828</v>
+        <v>2.2279299999354411E-2</v>
       </c>
       <c r="K32">
-        <v>6.3569525999919279</v>
-      </c>
-    </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
+        <v>4.575307499995688</v>
+      </c>
+      <c r="M32">
+        <f t="shared" si="0"/>
+        <v>76.736111111111256</v>
+      </c>
+      <c r="N32">
+        <f t="shared" si="1"/>
+        <v>349.70833333333326</v>
+      </c>
+    </row>
+    <row r="33" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>70000</v>
       </c>
       <c r="B33">
-        <v>0.99</v>
+        <v>0.95499999999999996</v>
       </c>
       <c r="C33">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="D33">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="E33">
         <v>32</v>
       </c>
       <c r="F33">
-        <v>2040.2222222222219</v>
+        <v>144</v>
       </c>
       <c r="G33">
-        <v>463.91666666666669</v>
+        <v>144</v>
       </c>
       <c r="H33">
-        <v>60.166666666666671</v>
+        <v>23</v>
       </c>
       <c r="I33">
-        <v>5.9099409000045853</v>
+        <v>4.3014274000015584</v>
       </c>
       <c r="J33">
-        <v>0.43952159999753349</v>
+        <v>2.216429999680258E-2</v>
       </c>
       <c r="K33">
-        <v>6.3494625000021188</v>
-      </c>
-    </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
+        <v>4.3235916999983601</v>
+      </c>
+      <c r="M33">
+        <f t="shared" si="0"/>
+        <v>205.70833333333326</v>
+      </c>
+      <c r="N33">
+        <f t="shared" si="1"/>
+        <v>349.70833333333326</v>
+      </c>
+    </row>
+    <row r="34" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>70000</v>
       </c>
       <c r="B34">
-        <v>0.99</v>
+        <v>0.95499999999999996</v>
       </c>
       <c r="C34">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="D34">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="E34">
         <v>33</v>
       </c>
       <c r="F34">
-        <v>2353.166666666667</v>
+        <v>359.97222222222229</v>
       </c>
       <c r="G34">
-        <v>720.97222222222206</v>
+        <v>359.97222222222229</v>
       </c>
       <c r="H34">
-        <v>91.472222222222214</v>
+        <v>51.111111111111128</v>
       </c>
       <c r="I34">
-        <v>5.9476276000059443</v>
+        <v>4.3094290000008186</v>
       </c>
       <c r="J34">
-        <v>0.35011290000693412</v>
+        <v>2.2420799999963489E-2</v>
       </c>
       <c r="K34">
-        <v>6.2977405000128783</v>
-      </c>
-    </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
+        <v>4.3318498000007821</v>
+      </c>
+      <c r="M34">
+        <f t="shared" si="0"/>
+        <v>10.263888888889028</v>
+      </c>
+      <c r="N34">
+        <f t="shared" si="1"/>
+        <v>349.70833333333326</v>
+      </c>
+    </row>
+    <row r="35" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>70000</v>
       </c>
       <c r="B35">
-        <v>0.99</v>
+        <v>0.95499999999999996</v>
       </c>
       <c r="C35">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="D35">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="E35">
         <v>34</v>
       </c>
       <c r="F35">
-        <v>2362.083333333333</v>
+        <v>471.50000000000011</v>
       </c>
       <c r="G35">
-        <v>595.19444444444457</v>
+        <v>471.50000000000011</v>
       </c>
       <c r="H35">
-        <v>88.000000000000014</v>
+        <v>50.277777777777793</v>
       </c>
       <c r="I35">
-        <v>5.9104904999985592</v>
+        <v>4.3737662000057753</v>
       </c>
       <c r="J35">
-        <v>0.33727649999491399</v>
+        <v>2.2894800000358369E-2</v>
       </c>
       <c r="K35">
-        <v>6.2477669999934733</v>
-      </c>
-    </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
+        <v>4.3966610000061337</v>
+      </c>
+      <c r="M35">
+        <f t="shared" si="0"/>
+        <v>121.79166666666686</v>
+      </c>
+      <c r="N35">
+        <f t="shared" si="1"/>
+        <v>349.70833333333326</v>
+      </c>
+    </row>
+    <row r="36" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>70000</v>
       </c>
       <c r="B36">
-        <v>0.99</v>
+        <v>0.95499999999999996</v>
       </c>
       <c r="C36">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="D36">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="E36">
         <v>35</v>
       </c>
       <c r="F36">
-        <v>2467.1944444444448</v>
+        <v>504.24999999999977</v>
       </c>
       <c r="G36">
-        <v>533</v>
+        <v>504.24999999999977</v>
       </c>
       <c r="H36">
-        <v>77.055555555555557</v>
+        <v>73.416666666666657</v>
       </c>
       <c r="I36">
-        <v>5.8558939999929862</v>
+        <v>4.260836700006621</v>
       </c>
       <c r="J36">
-        <v>0.76138630000059493</v>
+        <v>2.1456399990711361E-2</v>
       </c>
       <c r="K36">
-        <v>6.6172802999935811</v>
-      </c>
-    </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
+        <v>4.2822930999973323</v>
+      </c>
+      <c r="M36">
+        <f t="shared" si="0"/>
+        <v>154.54166666666652</v>
+      </c>
+      <c r="N36">
+        <f t="shared" si="1"/>
+        <v>349.70833333333326</v>
+      </c>
+    </row>
+    <row r="37" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>70000</v>
       </c>
       <c r="B37">
-        <v>0.99</v>
+        <v>0.95499999999999996</v>
       </c>
       <c r="C37">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="D37">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="E37">
         <v>36</v>
       </c>
       <c r="F37">
-        <v>2070.25</v>
+        <v>305.94444444444417</v>
       </c>
       <c r="G37">
-        <v>579.41666666666674</v>
+        <v>305.94444444444417</v>
       </c>
       <c r="H37">
-        <v>70.777777777777786</v>
+        <v>31.833333333333311</v>
       </c>
       <c r="I37">
-        <v>5.883093700002064</v>
+        <v>4.3506750999949872</v>
       </c>
       <c r="J37">
-        <v>0.56110249999619555</v>
+        <v>2.2731899996870201E-2</v>
       </c>
       <c r="K37">
-        <v>6.4441961999982604</v>
-      </c>
-    </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
+        <v>4.3734069999918566</v>
+      </c>
+      <c r="M37">
+        <f t="shared" si="0"/>
+        <v>43.763888888889085</v>
+      </c>
+      <c r="N37">
+        <f t="shared" si="1"/>
+        <v>349.70833333333326</v>
+      </c>
+    </row>
+    <row r="38" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>70000</v>
       </c>
       <c r="B38">
-        <v>0.99</v>
+        <v>0.95499999999999996</v>
       </c>
       <c r="C38">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="D38">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="E38">
         <v>37</v>
       </c>
       <c r="F38">
-        <v>2326.6944444444448</v>
+        <v>293.00000000000011</v>
       </c>
       <c r="G38">
-        <v>579.63888888888891</v>
+        <v>273.83333333333331</v>
       </c>
       <c r="H38">
-        <v>74.666666666666671</v>
+        <v>41.249999999999993</v>
       </c>
       <c r="I38">
-        <v>6.0156035999971209</v>
+        <v>4.3794996000069659</v>
       </c>
       <c r="J38">
-        <v>0.36597379999875562</v>
+        <v>6.3699599995743483E-2</v>
       </c>
       <c r="K38">
-        <v>6.3815773999958756</v>
-      </c>
-    </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
+        <v>4.4431992000027094</v>
+      </c>
+      <c r="M38">
+        <f t="shared" si="0"/>
+        <v>75.874999999999943</v>
+      </c>
+      <c r="N38">
+        <f t="shared" si="1"/>
+        <v>349.70833333333326</v>
+      </c>
+    </row>
+    <row r="39" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>70000</v>
       </c>
       <c r="B39">
-        <v>0.99</v>
+        <v>0.95499999999999996</v>
       </c>
       <c r="C39">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="D39">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="E39">
         <v>38</v>
       </c>
       <c r="F39">
-        <v>2072.0555555555561</v>
+        <v>501.94444444444468</v>
       </c>
       <c r="G39">
-        <v>977.63888888888914</v>
+        <v>501.94444444444468</v>
       </c>
       <c r="H39">
-        <v>130.13888888888891</v>
+        <v>53.194444444444457</v>
       </c>
       <c r="I39">
-        <v>5.9706547999958266</v>
+        <v>4.3372454999916954</v>
       </c>
       <c r="J39">
-        <v>0.36880869999004062</v>
+        <v>2.1949699992546812E-2</v>
       </c>
       <c r="K39">
-        <v>6.3394634999858681</v>
-      </c>
-    </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
+        <v>4.3591951999842422</v>
+      </c>
+      <c r="M39">
+        <f t="shared" si="0"/>
+        <v>152.23611111111143</v>
+      </c>
+      <c r="N39">
+        <f t="shared" si="1"/>
+        <v>349.70833333333326</v>
+      </c>
+    </row>
+    <row r="40" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>70000</v>
       </c>
       <c r="B40">
-        <v>0.99</v>
+        <v>0.95499999999999996</v>
       </c>
       <c r="C40">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="D40">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="E40">
         <v>39</v>
       </c>
       <c r="F40">
-        <v>2022.5</v>
+        <v>267.94444444444429</v>
       </c>
       <c r="G40">
-        <v>1153.583333333333</v>
+        <v>267.94444444444429</v>
       </c>
       <c r="H40">
-        <v>141.6944444444444</v>
+        <v>40.027777777777757</v>
       </c>
       <c r="I40">
-        <v>5.8715430999873206</v>
+        <v>4.2827115000109188</v>
       </c>
       <c r="J40">
-        <v>0.2388400000054389</v>
+        <v>2.2018800009391271E-2</v>
       </c>
       <c r="K40">
-        <v>6.1103830999927604</v>
-      </c>
-    </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
+        <v>4.3047303000203101</v>
+      </c>
+      <c r="M40">
+        <f t="shared" si="0"/>
+        <v>81.763888888888971</v>
+      </c>
+      <c r="N40">
+        <f t="shared" si="1"/>
+        <v>349.70833333333326</v>
+      </c>
+    </row>
+    <row r="41" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>70000</v>
       </c>
       <c r="B41">
-        <v>0.99</v>
+        <v>0.95499999999999996</v>
       </c>
       <c r="C41">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="D41">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="E41">
         <v>40</v>
       </c>
       <c r="F41">
-        <v>2308.4444444444439</v>
+        <v>398.58333333333331</v>
       </c>
       <c r="G41">
-        <v>992.91666666666652</v>
+        <v>398.58333333333331</v>
       </c>
       <c r="H41">
-        <v>114.8333333333333</v>
+        <v>59.80555555555555</v>
       </c>
       <c r="I41">
-        <v>5.8387920999957714</v>
+        <v>4.2708839000115404</v>
       </c>
       <c r="J41">
-        <v>0.50079730000288691</v>
+        <v>2.228560000366997E-2</v>
       </c>
       <c r="K41">
-        <v>6.3395893999986583</v>
-      </c>
-    </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.25">
+        <v>4.2931695000152104</v>
+      </c>
+      <c r="M41">
+        <f t="shared" si="0"/>
+        <v>48.875000000000057</v>
+      </c>
+      <c r="N41">
+        <f t="shared" si="1"/>
+        <v>349.70833333333326</v>
+      </c>
+    </row>
+    <row r="42" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>70000</v>
       </c>
       <c r="B42">
-        <v>0.99</v>
+        <v>0.95499999999999996</v>
       </c>
       <c r="C42">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="D42">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="E42">
         <v>41</v>
       </c>
       <c r="F42">
-        <v>1624.833333333333</v>
+        <v>337.00000000000011</v>
       </c>
       <c r="G42">
-        <v>861.72222222222183</v>
+        <v>337.00000000000011</v>
       </c>
       <c r="H42">
-        <v>123.6666666666666</v>
+        <v>49.527777777777779</v>
       </c>
       <c r="I42">
-        <v>5.9149316999973962</v>
+        <v>4.3617032000038307</v>
       </c>
       <c r="J42">
-        <v>0.25992799999949062</v>
+        <v>2.177009999286383E-2</v>
       </c>
       <c r="K42">
-        <v>6.1748596999968868</v>
-      </c>
-    </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.25">
+        <v>4.3834732999966954</v>
+      </c>
+      <c r="M42">
+        <f t="shared" si="0"/>
+        <v>12.708333333333144</v>
+      </c>
+      <c r="N42">
+        <f t="shared" si="1"/>
+        <v>349.70833333333326</v>
+      </c>
+    </row>
+    <row r="43" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>70000</v>
       </c>
       <c r="B43">
-        <v>0.99</v>
+        <v>0.95499999999999996</v>
       </c>
       <c r="C43">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="D43">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="E43">
         <v>42</v>
       </c>
       <c r="F43">
-        <v>2201.5277777777778</v>
+        <v>267.25</v>
       </c>
       <c r="G43">
-        <v>1371.194444444445</v>
+        <v>267.25</v>
       </c>
       <c r="H43">
-        <v>151.83333333333329</v>
+        <v>42.416666666666657</v>
       </c>
       <c r="I43">
-        <v>5.9491418999969028</v>
+        <v>4.268582000004244</v>
       </c>
       <c r="J43">
-        <v>0.27247999999963213</v>
+        <v>2.195569999457803E-2</v>
       </c>
       <c r="K43">
-        <v>6.2216218999965349</v>
-      </c>
-    </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.25">
+        <v>4.2905376999988221</v>
+      </c>
+      <c r="M43">
+        <f t="shared" si="0"/>
+        <v>82.458333333333258</v>
+      </c>
+      <c r="N43">
+        <f t="shared" si="1"/>
+        <v>349.70833333333326</v>
+      </c>
+    </row>
+    <row r="44" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>70000</v>
       </c>
       <c r="B44">
-        <v>0.99</v>
+        <v>0.95499999999999996</v>
       </c>
       <c r="C44">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="D44">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="E44">
         <v>43</v>
       </c>
       <c r="F44">
-        <v>2231.666666666667</v>
+        <v>460.13888888888903</v>
       </c>
       <c r="G44">
-        <v>686.33333333333337</v>
+        <v>460.13888888888903</v>
       </c>
       <c r="H44">
-        <v>97.444444444444457</v>
+        <v>64.305555555555571</v>
       </c>
       <c r="I44">
-        <v>5.9004247999982908</v>
+        <v>4.3977660000091419</v>
       </c>
       <c r="J44">
-        <v>0.57285620000038762</v>
+        <v>2.214979998825584E-2</v>
       </c>
       <c r="K44">
-        <v>6.4732809999986776</v>
-      </c>
-    </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.25">
+        <v>4.4199157999973977</v>
+      </c>
+      <c r="M44">
+        <f t="shared" si="0"/>
+        <v>110.43055555555577</v>
+      </c>
+      <c r="N44">
+        <f t="shared" si="1"/>
+        <v>349.70833333333326</v>
+      </c>
+    </row>
+    <row r="45" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>70000</v>
       </c>
       <c r="B45">
-        <v>0.99</v>
+        <v>0.95499999999999996</v>
       </c>
       <c r="C45">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="D45">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="E45">
         <v>44</v>
       </c>
       <c r="F45">
-        <v>2294.5</v>
+        <v>388.02777777777749</v>
       </c>
       <c r="G45">
-        <v>986.66666666666674</v>
+        <v>388.02777777777749</v>
       </c>
       <c r="H45">
-        <v>124.6944444444444</v>
+        <v>52.333333333333293</v>
       </c>
       <c r="I45">
-        <v>5.9524452999903588</v>
+        <v>4.2477335000003222</v>
       </c>
       <c r="J45">
-        <v>0.31639609999547252</v>
+        <v>2.1669299996574409E-2</v>
       </c>
       <c r="K45">
-        <v>6.2688413999858312</v>
-      </c>
-    </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.25">
+        <v>4.2694027999968966</v>
+      </c>
+      <c r="M45">
+        <f t="shared" si="0"/>
+        <v>38.31944444444423</v>
+      </c>
+      <c r="N45">
+        <f t="shared" si="1"/>
+        <v>349.70833333333326</v>
+      </c>
+    </row>
+    <row r="46" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>70000</v>
       </c>
       <c r="B46">
-        <v>0.99</v>
+        <v>0.95499999999999996</v>
       </c>
       <c r="C46">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="D46">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="E46">
         <v>45</v>
       </c>
       <c r="F46">
-        <v>2478.2777777777769</v>
+        <v>389.72222222222229</v>
       </c>
       <c r="G46">
-        <v>872.5277777777776</v>
+        <v>389.72222222222229</v>
       </c>
       <c r="H46">
-        <v>114.1666666666666</v>
+        <v>55.222222222222229</v>
       </c>
       <c r="I46">
-        <v>5.8670320999954129</v>
+        <v>4.3080220999981984</v>
       </c>
       <c r="J46">
-        <v>0.35277800000039861</v>
+        <v>2.3524799995357171E-2</v>
       </c>
       <c r="K46">
-        <v>6.2198100999958106</v>
-      </c>
-    </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.25">
+        <v>4.3315468999935547</v>
+      </c>
+      <c r="M46">
+        <f t="shared" si="0"/>
+        <v>40.013888888889028</v>
+      </c>
+      <c r="N46">
+        <f t="shared" si="1"/>
+        <v>349.70833333333326</v>
+      </c>
+    </row>
+    <row r="47" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>70000</v>
       </c>
       <c r="B47">
-        <v>0.99</v>
+        <v>0.95499999999999996</v>
       </c>
       <c r="C47">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="D47">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="E47">
         <v>46</v>
       </c>
       <c r="F47">
-        <v>1703</v>
+        <v>169.6666666666666</v>
       </c>
       <c r="G47">
-        <v>583.16666666666686</v>
+        <v>169.6666666666666</v>
       </c>
       <c r="H47">
-        <v>80.500000000000028</v>
+        <v>27.833333333333329</v>
       </c>
       <c r="I47">
-        <v>5.8632663000025786</v>
+        <v>4.2652508999890406</v>
       </c>
       <c r="J47">
-        <v>0.36729940000805072</v>
+        <v>2.2050300001865249E-2</v>
       </c>
       <c r="K47">
-        <v>6.2305657000106294</v>
-      </c>
-    </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.25">
+        <v>4.2873011999909068</v>
+      </c>
+      <c r="M47">
+        <f t="shared" si="0"/>
+        <v>180.04166666666666</v>
+      </c>
+      <c r="N47">
+        <f t="shared" si="1"/>
+        <v>349.70833333333326</v>
+      </c>
+    </row>
+    <row r="48" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>70000</v>
       </c>
       <c r="B48">
-        <v>0.99</v>
+        <v>0.95499999999999996</v>
       </c>
       <c r="C48">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="D48">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="E48">
         <v>47</v>
       </c>
       <c r="F48">
-        <v>2223</v>
+        <v>360.86111111111092</v>
       </c>
       <c r="G48">
-        <v>715.55555555555577</v>
+        <v>360.86111111111092</v>
       </c>
       <c r="H48">
-        <v>76.861111111111114</v>
+        <v>50.861111111111093</v>
       </c>
       <c r="I48">
-        <v>5.9455156999902101</v>
+        <v>4.2507688999903621</v>
       </c>
       <c r="J48">
-        <v>0.4016362999973353</v>
+        <v>2.2731600009137761E-2</v>
       </c>
       <c r="K48">
-        <v>6.3471519999875454</v>
-      </c>
-    </row>
-    <row r="49" spans="1:11" x14ac:dyDescent="0.25">
+        <v>4.2735004999994999</v>
+      </c>
+      <c r="M48">
+        <f t="shared" si="0"/>
+        <v>11.152777777777658</v>
+      </c>
+      <c r="N48">
+        <f t="shared" si="1"/>
+        <v>349.70833333333326</v>
+      </c>
+    </row>
+    <row r="49" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>70000</v>
       </c>
       <c r="B49">
-        <v>0.99</v>
+        <v>0.95499999999999996</v>
       </c>
       <c r="C49">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="D49">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="E49">
         <v>48</v>
       </c>
       <c r="F49">
-        <v>2173.166666666667</v>
+        <v>213.6111111111112</v>
       </c>
       <c r="G49">
-        <v>767.33333333333314</v>
+        <v>213.6111111111112</v>
       </c>
       <c r="H49">
-        <v>110.9722222222222</v>
+        <v>30.000000000000011</v>
       </c>
       <c r="I49">
-        <v>5.8595460000069579</v>
+        <v>4.3390712999971583</v>
       </c>
       <c r="J49">
-        <v>0.52261470000667032</v>
+        <v>2.2555200004717339E-2</v>
       </c>
       <c r="K49">
-        <v>6.3821607000136282</v>
-      </c>
-    </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.25">
+        <v>4.3616265000018757</v>
+      </c>
+      <c r="M49">
+        <f t="shared" si="0"/>
+        <v>136.09722222222206</v>
+      </c>
+      <c r="N49">
+        <f t="shared" si="1"/>
+        <v>349.70833333333326</v>
+      </c>
+    </row>
+    <row r="50" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>70000</v>
       </c>
       <c r="B50">
-        <v>0.99</v>
+        <v>0.95499999999999996</v>
       </c>
       <c r="C50">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="D50">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="E50">
         <v>49</v>
       </c>
       <c r="F50">
-        <v>1924.3888888888889</v>
+        <v>249.44444444444451</v>
       </c>
       <c r="G50">
-        <v>863.97222222222217</v>
+        <v>249.44444444444451</v>
       </c>
       <c r="H50">
-        <v>99.694444444444429</v>
+        <v>37.083333333333343</v>
       </c>
       <c r="I50">
-        <v>5.9249946000054479</v>
+        <v>4.1560023999918494</v>
       </c>
       <c r="J50">
-        <v>0.4089759999915259</v>
+        <v>2.2876899995026179E-2</v>
       </c>
       <c r="K50">
-        <v>6.3339705999969738</v>
-      </c>
-    </row>
-    <row r="51" spans="1:11" x14ac:dyDescent="0.25">
+        <v>4.1788792999868747</v>
+      </c>
+      <c r="M50">
+        <f t="shared" si="0"/>
+        <v>100.26388888888874</v>
+      </c>
+      <c r="N50">
+        <f t="shared" si="1"/>
+        <v>349.70833333333326</v>
+      </c>
+    </row>
+    <row r="51" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>70000</v>
       </c>
       <c r="B51">
-        <v>0.99</v>
+        <v>0.95499999999999996</v>
       </c>
       <c r="C51">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="D51">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="E51">
         <v>88</v>
       </c>
       <c r="F51">
-        <v>2400.8611111111109</v>
+        <v>433.83333333333343</v>
       </c>
       <c r="G51">
-        <v>707.72222222222229</v>
+        <v>433.83333333333343</v>
       </c>
       <c r="H51">
-        <v>94.694444444444443</v>
+        <v>51.361111111111121</v>
       </c>
       <c r="I51">
-        <v>5.8116068999952404</v>
+        <v>5.1256603999936488</v>
       </c>
       <c r="J51">
-        <v>0.43690449999121478</v>
+        <v>2.8741499991156161E-2</v>
       </c>
       <c r="K51">
-        <v>6.2485113999864552</v>
+        <v>5.1544018999848049</v>
+      </c>
+      <c r="M51">
+        <f t="shared" si="0"/>
+        <v>84.125000000000171</v>
+      </c>
+      <c r="N51">
+        <f t="shared" si="1"/>
+        <v>349.70833333333326</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/Experimenten5.xlsx
+++ b/Experimenten5.xlsx
@@ -15,7 +15,7 @@
   <sheets>
     <sheet name="Random seeds" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029" calcCompleted="0"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>

--- a/Experimenten5.xlsx
+++ b/Experimenten5.xlsx
@@ -8,13 +8,20 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://stichtingfontys-my.sharepoint.com/personal/582755_student_fontys_nl/Documents/Leerjaar 2/Periode 1/Operations Research 5/OR5/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="26" documentId="11_4419C470179018682943C3F0505ED87656CDA62E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5E4EB37B-4427-4221-8430-819D4794677D}"/>
+  <xr:revisionPtr revIDLastSave="81" documentId="11_2955C66E172019671D83DEF0505ED87656CDD67A" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{42A48DB8-5AB1-4FC9-A397-274384D3AC92}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Random seeds" sheetId="1" r:id="rId1"/>
+    <sheet name="Boxplot" sheetId="2" r:id="rId2"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlchart.v1.0" hidden="1">Boxplot!$B$1</definedName>
+    <definedName name="_xlchart.v1.1" hidden="1">Boxplot!$B$2:$B$51</definedName>
+    <definedName name="_xlchart.v1.2" hidden="1">Boxplot!$B$1</definedName>
+    <definedName name="_xlchart.v1.3" hidden="1">Boxplot!$B$2:$B$51</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -33,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="17">
   <si>
     <t>t_max</t>
   </si>
@@ -68,23 +75,40 @@
     <t>Totale rekentijd (s)</t>
   </si>
   <si>
-    <t>Gemiddelde penalty</t>
+    <t>Q1</t>
   </si>
   <si>
-    <t>Afstand tot gemiddelde</t>
+    <t>Q3</t>
+  </si>
+  <si>
+    <t>IQR</t>
+  </si>
+  <si>
+    <t>Ondergrens</t>
+  </si>
+  <si>
+    <t>Bovengrens</t>
+  </si>
+  <si>
+    <t>Uitschieter?</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial Unicode MS"/>
     </font>
   </fonts>
   <fills count="2">
@@ -107,8 +131,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -126,974 +151,156 @@
 </styleSheet>
 </file>
 
-<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
-  <c:date1904 val="0"/>
-  <c:lang val="en-GB"/>
-  <c:roundedCorners val="0"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
-      <c14:style val="102"/>
-    </mc:Choice>
-    <mc:Fallback>
-      <c:style val="2"/>
-    </mc:Fallback>
-  </mc:AlternateContent>
-  <c:chart>
-    <c:title>
-      <c:tx>
-        <c:rich>
-          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+<file path=xl/charts/chartEx1.xml><?xml version="1.0" encoding="utf-8"?>
+<cx:chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex">
+  <cx:chartData>
+    <cx:data id="0">
+      <cx:numDim type="val">
+        <cx:f>_xlchart.v1.1</cx:f>
+      </cx:numDim>
+    </cx:data>
+  </cx:chartData>
+  <cx:chart>
+    <cx:title pos="t" align="ctr" overlay="0">
+      <cx:tx>
+        <cx:txData>
+          <cx:v>Verdeling van de totale penalty over 50 random seeds</cx:v>
+        </cx:txData>
+      </cx:tx>
+      <cx:txPr>
+        <a:bodyPr spcFirstLastPara="1" vertOverflow="ellipsis" horzOverflow="overflow" wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr" rtl="0">
+            <a:defRPr/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1400" b="0" i="0" u="none" strike="noStrike" baseline="0">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:sysClr>
+              </a:solidFill>
+              <a:latin typeface="Calibri"/>
+            </a:rPr>
+            <a:t>Verdeling van de totale penalty over 50 random seeds</a:t>
+          </a:r>
+        </a:p>
+      </cx:txPr>
+    </cx:title>
+    <cx:plotArea>
+      <cx:plotAreaRegion>
+        <cx:series layoutId="boxWhisker" uniqueId="{00000000-D718-4270-8BB0-1D0416A9BF03}">
+          <cx:tx>
+            <cx:txData>
+              <cx:f>_xlchart.v1.0</cx:f>
+              <cx:v>Total penalty</cx:v>
+            </cx:txData>
+          </cx:tx>
+          <cx:dataId val="0"/>
+          <cx:layoutPr>
+            <cx:visibility meanLine="0" meanMarker="1" nonoutliers="0" outliers="1"/>
+            <cx:statistics quartileMethod="inclusive"/>
+          </cx:layoutPr>
+        </cx:series>
+      </cx:plotAreaRegion>
+      <cx:axis id="0">
+        <cx:catScaling gapWidth="1"/>
+        <cx:title>
+          <cx:txPr>
+            <a:bodyPr spcFirstLastPara="1" vertOverflow="ellipsis" horzOverflow="overflow" wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr algn="ctr" rtl="0">
+                <a:defRPr/>
+              </a:pPr>
+              <a:endParaRPr lang="en-GB" sz="900" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                <a:solidFill>
+                  <a:sysClr val="windowText" lastClr="000000">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:sysClr>
+                </a:solidFill>
+                <a:latin typeface="Calibri"/>
+              </a:endParaRPr>
+            </a:p>
+          </cx:txPr>
+        </cx:title>
+        <cx:tickLabels/>
+        <cx:txPr>
+          <a:bodyPr spcFirstLastPara="1" vertOverflow="ellipsis" horzOverflow="overflow" wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" anchor="ctr" anchorCtr="1"/>
           <a:lstStyle/>
           <a:p>
-            <a:pPr>
-              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
+            <a:pPr algn="ctr" rtl="0">
+              <a:defRPr sz="100"/>
             </a:pPr>
-            <a:r>
-              <a:rPr lang="nl-NL"/>
-              <a:t>Invloed van de random seed op de</a:t>
-            </a:r>
-            <a:r>
-              <a:rPr lang="nl-NL" baseline="0"/>
-              <a:t> totale penalty</a:t>
-            </a:r>
-          </a:p>
-        </c:rich>
-      </c:tx>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+            <a:endParaRPr lang="en-GB" sz="100" b="0" i="0" u="none" strike="noStrike" baseline="0">
               <a:solidFill>
-                <a:schemeClr val="tx1">
+                <a:sysClr val="windowText" lastClr="000000">
                   <a:lumMod val="65000"/>
                   <a:lumOff val="35000"/>
-                </a:schemeClr>
+                </a:sysClr>
               </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="nl-NL"/>
-        </a:p>
-      </c:txPr>
-    </c:title>
-    <c:autoTitleDeleted val="0"/>
-    <c:plotArea>
-      <c:layout/>
-      <c:scatterChart>
-        <c:scatterStyle val="lineMarker"/>
-        <c:varyColors val="0"/>
-        <c:ser>
-          <c:idx val="0"/>
-          <c:order val="0"/>
-          <c:tx>
-            <c:v>Totale penalty</c:v>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="25400" cap="rnd">
-              <a:noFill/>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="5"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:schemeClr val="accent1"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-          </c:marker>
-          <c:xVal>
-            <c:numRef>
-              <c:f>'Random seeds'!$E$2:$E$51</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="50"/>
-                <c:pt idx="0">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>2</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>3</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>4</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>5</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>6</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>7</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>8</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>9</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>10</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>11</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>12</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>13</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>14</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>15</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>16</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>17</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>18</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>19</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>20</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>21</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>22</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>23</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>24</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>25</c:v>
-                </c:pt>
-                <c:pt idx="25">
-                  <c:v>26</c:v>
-                </c:pt>
-                <c:pt idx="26">
-                  <c:v>27</c:v>
-                </c:pt>
-                <c:pt idx="27">
-                  <c:v>28</c:v>
-                </c:pt>
-                <c:pt idx="28">
-                  <c:v>29</c:v>
-                </c:pt>
-                <c:pt idx="29">
-                  <c:v>30</c:v>
-                </c:pt>
-                <c:pt idx="30">
-                  <c:v>31</c:v>
-                </c:pt>
-                <c:pt idx="31">
-                  <c:v>32</c:v>
-                </c:pt>
-                <c:pt idx="32">
-                  <c:v>33</c:v>
-                </c:pt>
-                <c:pt idx="33">
-                  <c:v>34</c:v>
-                </c:pt>
-                <c:pt idx="34">
-                  <c:v>35</c:v>
-                </c:pt>
-                <c:pt idx="35">
-                  <c:v>36</c:v>
-                </c:pt>
-                <c:pt idx="36">
-                  <c:v>37</c:v>
-                </c:pt>
-                <c:pt idx="37">
-                  <c:v>38</c:v>
-                </c:pt>
-                <c:pt idx="38">
-                  <c:v>39</c:v>
-                </c:pt>
-                <c:pt idx="39">
-                  <c:v>40</c:v>
-                </c:pt>
-                <c:pt idx="40">
-                  <c:v>41</c:v>
-                </c:pt>
-                <c:pt idx="41">
-                  <c:v>42</c:v>
-                </c:pt>
-                <c:pt idx="42">
-                  <c:v>43</c:v>
-                </c:pt>
-                <c:pt idx="43">
-                  <c:v>44</c:v>
-                </c:pt>
-                <c:pt idx="44">
-                  <c:v>45</c:v>
-                </c:pt>
-                <c:pt idx="45">
-                  <c:v>46</c:v>
-                </c:pt>
-                <c:pt idx="46">
-                  <c:v>47</c:v>
-                </c:pt>
-                <c:pt idx="47">
-                  <c:v>48</c:v>
-                </c:pt>
-                <c:pt idx="48">
-                  <c:v>49</c:v>
-                </c:pt>
-                <c:pt idx="49">
-                  <c:v>88</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:xVal>
-          <c:yVal>
-            <c:numRef>
-              <c:f>'Random seeds'!$G$2:$G$51</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="50"/>
-                <c:pt idx="0">
-                  <c:v>156.0555555555556</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>370.58333333333343</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>460.08333333333331</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>371.61111111111109</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>267.25</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>294.52777777777783</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>445.41666666666657</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>520.7222222222224</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>288.05555555555537</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>519.27777777777783</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>329.5833333333332</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>420.27777777777771</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>206.33333333333329</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>252.1666666666668</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>282.80555555555549</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>292.8888888888888</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>389.77777777777811</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>253.25</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>298.49999999999989</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>379.49999999999989</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>560.58333333333337</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>316.55555555555571</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>419.6111111111112</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>282.33333333333343</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>353.99999999999989</c:v>
-                </c:pt>
-                <c:pt idx="25">
-                  <c:v>288.38888888888891</c:v>
-                </c:pt>
-                <c:pt idx="26">
-                  <c:v>294.50000000000011</c:v>
-                </c:pt>
-                <c:pt idx="27">
-                  <c:v>394.88888888888869</c:v>
-                </c:pt>
-                <c:pt idx="28">
-                  <c:v>458.91666666666652</c:v>
-                </c:pt>
-                <c:pt idx="29">
-                  <c:v>393</c:v>
-                </c:pt>
-                <c:pt idx="30">
-                  <c:v>426.44444444444451</c:v>
-                </c:pt>
-                <c:pt idx="31">
-                  <c:v>144</c:v>
-                </c:pt>
-                <c:pt idx="32">
-                  <c:v>359.97222222222229</c:v>
-                </c:pt>
-                <c:pt idx="33">
-                  <c:v>471.50000000000011</c:v>
-                </c:pt>
-                <c:pt idx="34">
-                  <c:v>504.24999999999977</c:v>
-                </c:pt>
-                <c:pt idx="35">
-                  <c:v>305.94444444444417</c:v>
-                </c:pt>
-                <c:pt idx="36">
-                  <c:v>273.83333333333331</c:v>
-                </c:pt>
-                <c:pt idx="37">
-                  <c:v>501.94444444444468</c:v>
-                </c:pt>
-                <c:pt idx="38">
-                  <c:v>267.94444444444429</c:v>
-                </c:pt>
-                <c:pt idx="39">
-                  <c:v>398.58333333333331</c:v>
-                </c:pt>
-                <c:pt idx="40">
-                  <c:v>337.00000000000011</c:v>
-                </c:pt>
-                <c:pt idx="41">
-                  <c:v>267.25</c:v>
-                </c:pt>
-                <c:pt idx="42">
-                  <c:v>460.13888888888903</c:v>
-                </c:pt>
-                <c:pt idx="43">
-                  <c:v>388.02777777777749</c:v>
-                </c:pt>
-                <c:pt idx="44">
-                  <c:v>389.72222222222229</c:v>
-                </c:pt>
-                <c:pt idx="45">
-                  <c:v>169.6666666666666</c:v>
-                </c:pt>
-                <c:pt idx="46">
-                  <c:v>360.86111111111092</c:v>
-                </c:pt>
-                <c:pt idx="47">
-                  <c:v>213.6111111111112</c:v>
-                </c:pt>
-                <c:pt idx="48">
-                  <c:v>249.44444444444451</c:v>
-                </c:pt>
-                <c:pt idx="49">
-                  <c:v>433.83333333333343</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:yVal>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-16AF-4FCC-8A9D-4CE30B2AB55F}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="1"/>
-          <c:order val="1"/>
-          <c:tx>
-            <c:v>Gemiddelde penalty</c:v>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="25400" cap="rnd">
-              <a:noFill/>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="5"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent2"/>
-              </a:solidFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:schemeClr val="accent2"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-          </c:marker>
-          <c:xVal>
-            <c:numRef>
-              <c:f>'Random seeds'!$E$2:$E$51</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="50"/>
-                <c:pt idx="0">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>2</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>3</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>4</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>5</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>6</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>7</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>8</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>9</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>10</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>11</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>12</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>13</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>14</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>15</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>16</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>17</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>18</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>19</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>20</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>21</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>22</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>23</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>24</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>25</c:v>
-                </c:pt>
-                <c:pt idx="25">
-                  <c:v>26</c:v>
-                </c:pt>
-                <c:pt idx="26">
-                  <c:v>27</c:v>
-                </c:pt>
-                <c:pt idx="27">
-                  <c:v>28</c:v>
-                </c:pt>
-                <c:pt idx="28">
-                  <c:v>29</c:v>
-                </c:pt>
-                <c:pt idx="29">
-                  <c:v>30</c:v>
-                </c:pt>
-                <c:pt idx="30">
-                  <c:v>31</c:v>
-                </c:pt>
-                <c:pt idx="31">
-                  <c:v>32</c:v>
-                </c:pt>
-                <c:pt idx="32">
-                  <c:v>33</c:v>
-                </c:pt>
-                <c:pt idx="33">
-                  <c:v>34</c:v>
-                </c:pt>
-                <c:pt idx="34">
-                  <c:v>35</c:v>
-                </c:pt>
-                <c:pt idx="35">
-                  <c:v>36</c:v>
-                </c:pt>
-                <c:pt idx="36">
-                  <c:v>37</c:v>
-                </c:pt>
-                <c:pt idx="37">
-                  <c:v>38</c:v>
-                </c:pt>
-                <c:pt idx="38">
-                  <c:v>39</c:v>
-                </c:pt>
-                <c:pt idx="39">
-                  <c:v>40</c:v>
-                </c:pt>
-                <c:pt idx="40">
-                  <c:v>41</c:v>
-                </c:pt>
-                <c:pt idx="41">
-                  <c:v>42</c:v>
-                </c:pt>
-                <c:pt idx="42">
-                  <c:v>43</c:v>
-                </c:pt>
-                <c:pt idx="43">
-                  <c:v>44</c:v>
-                </c:pt>
-                <c:pt idx="44">
-                  <c:v>45</c:v>
-                </c:pt>
-                <c:pt idx="45">
-                  <c:v>46</c:v>
-                </c:pt>
-                <c:pt idx="46">
-                  <c:v>47</c:v>
-                </c:pt>
-                <c:pt idx="47">
-                  <c:v>48</c:v>
-                </c:pt>
-                <c:pt idx="48">
-                  <c:v>49</c:v>
-                </c:pt>
-                <c:pt idx="49">
-                  <c:v>88</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:xVal>
-          <c:yVal>
-            <c:numRef>
-              <c:f>'Random seeds'!$N$47</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>349.70833333333326</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:yVal>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-16AF-4FCC-8A9D-4CE30B2AB55F}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:dLbls>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-        </c:dLbls>
-        <c:axId val="1410300847"/>
-        <c:axId val="713260047"/>
-      </c:scatterChart>
-      <c:valAx>
-        <c:axId val="1410300847"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="b"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:majorGridlines>
-        <c:title>
-          <c:tx>
-            <c:rich>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                    <a:solidFill>
-                      <a:schemeClr val="tx1">
-                        <a:lumMod val="65000"/>
-                        <a:lumOff val="35000"/>
-                      </a:schemeClr>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                    <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="+mn-cs"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:r>
-                  <a:rPr lang="nl-NL" sz="1200"/>
-                  <a:t>Random</a:t>
-                </a:r>
-                <a:r>
-                  <a:rPr lang="nl-NL" sz="1200" baseline="0"/>
-                  <a:t> seed</a:t>
-                </a:r>
-              </a:p>
-            </c:rich>
-          </c:tx>
-          <c:overlay val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:latin typeface="Calibri"/>
+            </a:endParaRPr>
+          </a:p>
+        </cx:txPr>
+      </cx:axis>
+      <cx:axis id="1">
+        <cx:valScaling/>
+        <cx:title>
+          <cx:tx>
+            <cx:txData>
+              <cx:v>Totale penalty</cx:v>
+            </cx:txData>
+          </cx:tx>
+          <cx:txPr>
+            <a:bodyPr spcFirstLastPara="1" vertOverflow="ellipsis" horzOverflow="overflow" wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" anchor="ctr" anchorCtr="1"/>
             <a:lstStyle/>
             <a:p>
-              <a:pPr>
-                <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:pPr algn="ctr" rtl="0">
+                <a:defRPr sz="1200"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-GB" sz="1200" b="0" i="0" u="none" strike="noStrike" baseline="0">
                   <a:solidFill>
-                    <a:schemeClr val="tx1">
+                    <a:sysClr val="windowText" lastClr="000000">
                       <a:lumMod val="65000"/>
                       <a:lumOff val="35000"/>
-                    </a:schemeClr>
+                    </a:sysClr>
                   </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="nl-NL"/>
+                  <a:latin typeface="Calibri"/>
+                </a:rPr>
+                <a:t>Totale penalty</a:t>
+              </a:r>
             </a:p>
-          </c:txPr>
-        </c:title>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="25000"/>
-                <a:lumOff val="75000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          </cx:txPr>
+        </cx:title>
+        <cx:majorGridlines/>
+        <cx:tickLabels/>
+        <cx:txPr>
+          <a:bodyPr spcFirstLastPara="1" vertOverflow="ellipsis" horzOverflow="overflow" wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" anchor="ctr" anchorCtr="1"/>
           <a:lstStyle/>
           <a:p>
-            <a:pPr>
-              <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
+            <a:pPr algn="ctr" rtl="0">
+              <a:defRPr sz="1200"/>
             </a:pPr>
-            <a:endParaRPr lang="nl-NL"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="713260047"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="midCat"/>
-      </c:valAx>
-      <c:valAx>
-        <c:axId val="713260047"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="l"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:endParaRPr lang="en-GB" sz="1200" b="0" i="0" u="none" strike="noStrike" baseline="0">
               <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:majorGridlines>
-        <c:title>
-          <c:tx>
-            <c:rich>
-              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                    <a:solidFill>
-                      <a:schemeClr val="tx1">
-                        <a:lumMod val="65000"/>
-                        <a:lumOff val="35000"/>
-                      </a:schemeClr>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                    <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="+mn-cs"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:r>
-                  <a:rPr lang="nl-NL" sz="1200"/>
-                  <a:t>Totale penalty</a:t>
-                </a:r>
-              </a:p>
-            </c:rich>
-          </c:tx>
-          <c:overlay val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="65000"/>
-                      <a:lumOff val="35000"/>
-                    </a:schemeClr>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="nl-NL"/>
-            </a:p>
-          </c:txPr>
-        </c:title>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="25000"/>
-                <a:lumOff val="75000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="nl-NL"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="1410300847"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="midCat"/>
-      </c:valAx>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-    </c:plotArea>
-    <c:legend>
-      <c:legendPos val="b"/>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
+                <a:sysClr val="windowText" lastClr="000000">
                   <a:lumMod val="65000"/>
                   <a:lumOff val="35000"/>
-                </a:schemeClr>
+                </a:sysClr>
               </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="nl-NL"/>
-        </a:p>
-      </c:txPr>
-    </c:legend>
-    <c:plotVisOnly val="1"/>
-    <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
-    <c:extLst>
-      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
-        <c16r3:dataDisplayOptions16>
-          <c16r3:dispNaAsBlank val="1"/>
-        </c16r3:dataDisplayOptions16>
-      </c:ext>
-    </c:extLst>
-  </c:chart>
-  <c:spPr>
-    <a:solidFill>
-      <a:schemeClr val="bg1"/>
-    </a:solidFill>
-    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-      <a:solidFill>
-        <a:schemeClr val="tx1">
-          <a:lumMod val="15000"/>
-          <a:lumOff val="85000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:round/>
-    </a:ln>
-    <a:effectLst/>
-  </c:spPr>
-  <c:txPr>
-    <a:bodyPr/>
-    <a:lstStyle/>
-    <a:p>
-      <a:pPr>
-        <a:defRPr/>
-      </a:pPr>
-      <a:endParaRPr lang="nl-NL"/>
-    </a:p>
-  </c:txPr>
-  <c:printSettings>
-    <c:headerFooter/>
-    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
-    <c:pageSetup/>
-  </c:printSettings>
-</c:chartSpace>
+              <a:latin typeface="Calibri"/>
+            </a:endParaRPr>
+          </a:p>
+        </cx:txPr>
+      </cx:axis>
+    </cx:plotArea>
+  </cx:chart>
+</cx:chartSpace>
 </file>
 
 <file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1137,7 +344,7 @@
 </file>
 
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="406">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
@@ -1148,7 +355,7 @@
         <a:lumOff val="35000"/>
       </a:schemeClr>
     </cs:fontRef>
-    <cs:defRPr sz="1000" kern="1200"/>
+    <cs:defRPr sz="900"/>
   </cs:axisTitle>
   <cs:categoryAxis>
     <cs:lnRef idx="0"/>
@@ -1164,14 +371,14 @@
       <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
           <a:schemeClr val="tx1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
           </a:schemeClr>
         </a:solidFill>
         <a:round/>
       </a:ln>
     </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
+    <cs:defRPr sz="900"/>
   </cs:categoryAxis>
   <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
     <cs:lnRef idx="0"/>
@@ -1194,7 +401,7 @@
         <a:round/>
       </a:ln>
     </cs:spPr>
-    <cs:defRPr sz="1000" kern="1200"/>
+    <cs:defRPr sz="1000"/>
   </cs:chartArea>
   <cs:dataLabel>
     <cs:lnRef idx="0"/>
@@ -1202,11 +409,11 @@
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1">
-        <a:lumMod val="75000"/>
-        <a:lumOff val="25000"/>
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
       </a:schemeClr>
     </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
+    <cs:defRPr sz="900"/>
   </cs:dataLabel>
   <cs:dataLabelCallout>
     <cs:lnRef idx="0"/>
@@ -1231,42 +438,59 @@
         </a:solidFill>
       </a:ln>
     </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
+    <cs:defRPr sz="900"/>
     <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
       <a:spAutoFit/>
     </cs:bodyPr>
   </cs:dataLabelCallout>
   <cs:dataPoint>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="1">
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:fillRef>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
   </cs:dataPoint>
   <cs:dataPoint3D>
     <cs:lnRef idx="0"/>
-    <cs:fillRef idx="1">
+    <cs:fillRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:fillRef>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
   </cs:dataPoint3D>
   <cs:dataPointLine>
     <cs:lnRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:lnRef>
-    <cs:fillRef idx="1"/>
+    <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="19050" cap="rnd">
+      <a:ln w="28575" cap="rnd">
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
@@ -1275,10 +499,8 @@
     </cs:spPr>
   </cs:dataPointLine>
   <cs:dataPointMarker>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="1">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:fillRef>
     <cs:effectRef idx="0"/>
@@ -1286,9 +508,12 @@
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
       <a:ln w="9525">
         <a:solidFill>
-          <a:schemeClr val="phClr"/>
+          <a:schemeClr val="lt1"/>
         </a:solidFill>
       </a:ln>
     </cs:spPr>
@@ -1301,10 +526,10 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="9525" cap="rnd">
+      <a:ln w="28575" cap="rnd">
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
@@ -1323,41 +548,38 @@
       </a:schemeClr>
     </cs:fontRef>
     <cs:spPr>
-      <a:noFill/>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:ln w="9525">
         <a:solidFill>
           <a:schemeClr val="tx1">
             <a:lumMod val="15000"/>
             <a:lumOff val="85000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:round/>
       </a:ln>
     </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
+    <cs:defRPr sz="900"/>
   </cs:dataTable>
   <cs:downBar>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:solidFill>
         <a:schemeClr val="dk1">
-          <a:lumMod val="75000"/>
-          <a:lumOff val="25000"/>
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
         </a:schemeClr>
       </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:ln w="9525">
         <a:solidFill>
           <a:schemeClr val="tx1">
             <a:lumMod val="65000"/>
             <a:lumOff val="35000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:downBar>
@@ -1406,12 +628,6 @@
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln>
-        <a:noFill/>
-      </a:ln>
-    </cs:spPr>
   </cs:floor>
   <cs:gridlineMajor>
     <cs:lnRef idx="0"/>
@@ -1443,8 +659,8 @@
       <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
           <a:schemeClr val="tx1">
-            <a:lumMod val="5000"/>
-            <a:lumOff val="95000"/>
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
           </a:schemeClr>
         </a:solidFill>
         <a:round/>
@@ -1462,8 +678,8 @@
       <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
           <a:schemeClr val="tx1">
-            <a:lumMod val="50000"/>
-            <a:lumOff val="50000"/>
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
           </a:schemeClr>
         </a:solidFill>
         <a:round/>
@@ -1499,7 +715,7 @@
         <a:lumOff val="35000"/>
       </a:schemeClr>
     </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
+    <cs:defRPr sz="900"/>
   </cs:legend>
   <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
     <cs:lnRef idx="0"/>
@@ -1527,7 +743,18 @@
         <a:lumOff val="35000"/>
       </a:schemeClr>
     </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900"/>
   </cs:seriesAxis>
   <cs:seriesLine>
     <cs:lnRef idx="0"/>
@@ -1537,12 +764,9 @@
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:ln w="9525" cap="flat">
         <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
+          <a:srgbClr val="D9D9D9"/>
         </a:solidFill>
         <a:round/>
       </a:ln>
@@ -1558,7 +782,7 @@
         <a:lumOff val="35000"/>
       </a:schemeClr>
     </cs:fontRef>
-    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+    <cs:defRPr sz="1400"/>
   </cs:title>
   <cs:trendline>
     <cs:lnRef idx="0">
@@ -1574,7 +798,7 @@
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:prstDash val="sysDot"/>
+        <a:prstDash val="sysDash"/>
       </a:ln>
     </cs:spPr>
   </cs:trendline>
@@ -1588,27 +812,26 @@
         <a:lumOff val="35000"/>
       </a:schemeClr>
     </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
+    <cs:defRPr sz="900"/>
   </cs:trendlineLabel>
   <cs:upBar>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:solidFill>
         <a:schemeClr val="lt1"/>
       </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:ln w="9525">
         <a:solidFill>
           <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:upBar>
@@ -1622,18 +845,7 @@
         <a:lumOff val="35000"/>
       </a:schemeClr>
     </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
+    <cs:defRPr sz="900"/>
   </cs:valueAxis>
   <cs:wall>
     <cs:lnRef idx="0"/>
@@ -1642,12 +854,6 @@
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln>
-        <a:noFill/>
-      </a:ln>
-    </cs:spPr>
   </cs:wall>
 </cs:chartStyle>
 </file>
@@ -1656,38 +862,284 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>247650</xdr:colOff>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>57150</xdr:colOff>
       <xdr:row>1</xdr:row>
-      <xdr:rowOff>95250</xdr:rowOff>
+      <xdr:rowOff>138111</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>29</xdr:col>
-      <xdr:colOff>95250</xdr:colOff>
-      <xdr:row>33</xdr:row>
-      <xdr:rowOff>38100</xdr:rowOff>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>171450</xdr:rowOff>
     </xdr:to>
-    <xdr:graphicFrame macro="">
-      <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="3" name="Chart 2">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" Requires="cx1">
+        <xdr:graphicFrame macro="">
+          <xdr:nvGraphicFramePr>
+            <xdr:cNvPr id="3" name="Chart 2">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{02B83A56-3DD5-A437-B8AE-886EFC95869F}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvGraphicFramePr/>
+          </xdr:nvGraphicFramePr>
+          <xdr:xfrm>
+            <a:off x="0" y="0"/>
+            <a:ext cx="0" cy="0"/>
+          </xdr:xfrm>
+          <a:graphic>
+            <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2014/chartex">
+              <cx:chart xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+            </a:graphicData>
+          </a:graphic>
+        </xdr:graphicFrame>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="0" name=""/>
+            <xdr:cNvSpPr>
+              <a:spLocks noTextEdit="1"/>
+            </xdr:cNvSpPr>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="5753100" y="328611"/>
+              <a:ext cx="4819650" cy="5557839"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:prstClr val="white"/>
+            </a:solidFill>
+            <a:ln w="1">
+              <a:solidFill>
+                <a:prstClr val="green"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:r>
+                <a:rPr lang="nl-NL" sz="1100"/>
+                <a:t>This chart isn’t available in your version of Excel.
+Editing this shape or saving this workbook into a different file format will permanently break the chart.</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>495299</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>85723</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>600075</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>142874</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="4" name="TextBox 3">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{35A03034-913D-0933-D1B8-F58A44C7A09A}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DE19F886-B4BF-DA7D-6EAD-BEC3801B86B4}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
-        <xdr:cNvGraphicFramePr/>
-      </xdr:nvGraphicFramePr>
-      <xdr:xfrm>
-        <a:off x="0" y="0"/>
-        <a:ext cx="0" cy="0"/>
-      </xdr:xfrm>
-      <a:graphic>
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-        </a:graphicData>
-      </a:graphic>
-    </xdr:graphicFrame>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6800849" y="847723"/>
+          <a:ext cx="1323976" cy="247651"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525" cmpd="sng">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="nl-NL" sz="1100">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>Seed 41 (623)</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>495299</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>9523</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>600075</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>66674</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="5" name="TextBox 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4D91FB26-CBD1-4BDC-B065-7E13DD1228EB}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6800849" y="1152523"/>
+          <a:ext cx="1323976" cy="247651"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525" cmpd="sng">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="nl-NL" sz="1100">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>Seed 16 (612,91)</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>542925</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>157161</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>38101</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>23812</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="6" name="TextBox 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A5661629-7950-458E-BCDE-1D5C1185BB54}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6848475" y="1490661"/>
+          <a:ext cx="1323976" cy="247651"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525" cmpd="sng">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="nl-NL" sz="1100">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>Seed 48 (548,08)</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
@@ -1978,8 +1430,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N51"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:K51"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="6.42578125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="13.7109375" bestFit="1" customWidth="1"/>
@@ -1992,11 +1444,9 @@
     <col min="9" max="9" width="15.140625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="28.5703125" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="18.140625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="19.42578125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="22.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2030,14 +1480,8 @@
       <c r="K1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:11">
       <c r="A2">
         <v>70000</v>
       </c>
@@ -2048,43 +1492,31 @@
         <v>700</v>
       </c>
       <c r="D2">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="E2">
         <v>1</v>
       </c>
       <c r="F2">
-        <v>156.0555555555556</v>
+        <v>287.5</v>
       </c>
       <c r="G2">
-        <v>156.0555555555556</v>
+        <v>287.5</v>
       </c>
       <c r="H2">
-        <v>17.972222222222229</v>
+        <v>42</v>
       </c>
       <c r="I2">
-        <v>4.2945706000027712</v>
+        <v>5.1146798999980092</v>
       </c>
       <c r="J2">
-        <v>3.4835400001611561E-2</v>
+        <v>2.607350000471342E-2</v>
       </c>
       <c r="K2">
-        <v>4.3294060000043828</v>
-      </c>
-      <c r="L2">
-        <f>AVERAGE($G$2:$G$51)</f>
-        <v>349.70833333333326</v>
-      </c>
-      <c r="M2">
-        <f>ABS(G2-$L$2)</f>
-        <v>193.65277777777766</v>
-      </c>
-      <c r="N2">
-        <f>$L$2</f>
-        <v>349.70833333333326</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+        <v>5.1407534000027226</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11">
       <c r="A3">
         <v>70000</v>
       </c>
@@ -2095,39 +1527,31 @@
         <v>700</v>
       </c>
       <c r="D3">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="E3">
         <v>2</v>
       </c>
       <c r="F3">
-        <v>370.58333333333343</v>
+        <v>384.2777777777776</v>
       </c>
       <c r="G3">
-        <v>370.58333333333343</v>
+        <v>374.2777777777776</v>
       </c>
       <c r="H3">
-        <v>55.138888888888893</v>
+        <v>53.749999999999972</v>
       </c>
       <c r="I3">
-        <v>4.6066441000002669</v>
+        <v>5.0022122999944258</v>
       </c>
       <c r="J3">
-        <v>2.6499399988097139E-2</v>
+        <v>4.7137999994447448E-2</v>
       </c>
       <c r="K3">
-        <v>4.6331434999883641</v>
-      </c>
-      <c r="M3">
-        <f t="shared" ref="M3:M51" si="0">ABS(G3-$L$2)</f>
-        <v>20.875000000000171</v>
-      </c>
-      <c r="N3">
-        <f t="shared" ref="N3:N51" si="1">$L$2</f>
-        <v>349.70833333333326</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+        <v>5.0493502999888733</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11">
       <c r="A4">
         <v>70000</v>
       </c>
@@ -2138,39 +1562,31 @@
         <v>700</v>
       </c>
       <c r="D4">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="E4">
         <v>3</v>
       </c>
       <c r="F4">
-        <v>483.33333333333331</v>
+        <v>248.0833333333334</v>
       </c>
       <c r="G4">
-        <v>460.08333333333331</v>
+        <v>248.0833333333334</v>
       </c>
       <c r="H4">
-        <v>67.249999999999986</v>
+        <v>22.583333333333339</v>
       </c>
       <c r="I4">
-        <v>4.5204039999953238</v>
+        <v>5.0101730000023963</v>
       </c>
       <c r="J4">
-        <v>4.8616200001561083E-2</v>
+        <v>2.8986399993300441E-2</v>
       </c>
       <c r="K4">
-        <v>4.5690201999968849</v>
-      </c>
-      <c r="M4">
-        <f t="shared" si="0"/>
-        <v>110.37500000000006</v>
-      </c>
-      <c r="N4">
-        <f t="shared" si="1"/>
-        <v>349.70833333333326</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+        <v>5.0391593999956967</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11">
       <c r="A5">
         <v>70000</v>
       </c>
@@ -2181,39 +1597,31 @@
         <v>700</v>
       </c>
       <c r="D5">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="E5">
         <v>4</v>
       </c>
       <c r="F5">
-        <v>371.61111111111109</v>
+        <v>309.27777777777783</v>
       </c>
       <c r="G5">
-        <v>371.61111111111109</v>
+        <v>309.27777777777783</v>
       </c>
       <c r="H5">
-        <v>56.333333333333343</v>
+        <v>40.111111111111121</v>
       </c>
       <c r="I5">
-        <v>4.4489886000083061</v>
+        <v>5.7662630999984694</v>
       </c>
       <c r="J5">
-        <v>2.6855700009036809E-2</v>
+        <v>3.0209999997168779E-2</v>
       </c>
       <c r="K5">
-        <v>4.4758443000173429</v>
-      </c>
-      <c r="M5">
-        <f t="shared" si="0"/>
-        <v>21.902777777777828</v>
-      </c>
-      <c r="N5">
-        <f t="shared" si="1"/>
-        <v>349.70833333333326</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+        <v>5.7964730999956373</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11">
       <c r="A6">
         <v>70000</v>
       </c>
@@ -2224,39 +1632,31 @@
         <v>700</v>
       </c>
       <c r="D6">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="E6">
         <v>5</v>
       </c>
       <c r="F6">
-        <v>267.25</v>
+        <v>249.3888888888886</v>
       </c>
       <c r="G6">
-        <v>267.25</v>
+        <v>249.3888888888886</v>
       </c>
       <c r="H6">
-        <v>42.416666666666657</v>
+        <v>38.416666666666643</v>
       </c>
       <c r="I6">
-        <v>4.4760458999953698</v>
+        <v>5.3464142999873729</v>
       </c>
       <c r="J6">
-        <v>2.5460699995164759E-2</v>
+        <v>2.72153999976581E-2</v>
       </c>
       <c r="K6">
-        <v>4.5015065999905346</v>
-      </c>
-      <c r="M6">
-        <f t="shared" si="0"/>
-        <v>82.458333333333258</v>
-      </c>
-      <c r="N6">
-        <f t="shared" si="1"/>
-        <v>349.70833333333326</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+        <v>5.373629699985031</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11">
       <c r="A7">
         <v>70000</v>
       </c>
@@ -2267,39 +1667,31 @@
         <v>700</v>
       </c>
       <c r="D7">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="E7">
         <v>6</v>
       </c>
       <c r="F7">
-        <v>294.52777777777783</v>
+        <v>306.00000000000023</v>
       </c>
       <c r="G7">
-        <v>294.52777777777783</v>
+        <v>306.00000000000023</v>
       </c>
       <c r="H7">
-        <v>43.694444444444443</v>
+        <v>42.666666666666693</v>
       </c>
       <c r="I7">
-        <v>4.5316634000046179</v>
+        <v>6.1012235999951372</v>
       </c>
       <c r="J7">
-        <v>2.4096699999063279E-2</v>
+        <v>5.2981999993789941E-2</v>
       </c>
       <c r="K7">
-        <v>4.5557601000036811</v>
-      </c>
-      <c r="M7">
-        <f t="shared" si="0"/>
-        <v>55.180555555555429</v>
-      </c>
-      <c r="N7">
-        <f t="shared" si="1"/>
-        <v>349.70833333333326</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+        <v>6.1542055999889271</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11">
       <c r="A8">
         <v>70000</v>
       </c>
@@ -2310,39 +1702,31 @@
         <v>700</v>
       </c>
       <c r="D8">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="E8">
         <v>7</v>
       </c>
       <c r="F8">
-        <v>445.41666666666657</v>
+        <v>533.33333333333326</v>
       </c>
       <c r="G8">
-        <v>445.41666666666657</v>
+        <v>533.33333333333326</v>
       </c>
       <c r="H8">
-        <v>59.583333333333329</v>
+        <v>74.861111111111086</v>
       </c>
       <c r="I8">
-        <v>4.1914077999972514</v>
+        <v>5.5241670999967027</v>
       </c>
       <c r="J8">
-        <v>3.5960499997599982E-2</v>
+        <v>3.0947099992772561E-2</v>
       </c>
       <c r="K8">
-        <v>4.2273682999948514</v>
-      </c>
-      <c r="M8">
-        <f t="shared" si="0"/>
-        <v>95.708333333333314</v>
-      </c>
-      <c r="N8">
-        <f t="shared" si="1"/>
-        <v>349.70833333333326</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+        <v>5.5551141999894753</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11">
       <c r="A9">
         <v>70000</v>
       </c>
@@ -2353,39 +1737,31 @@
         <v>700</v>
       </c>
       <c r="D9">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="E9">
         <v>8</v>
       </c>
       <c r="F9">
-        <v>520.7222222222224</v>
+        <v>333.33333333333343</v>
       </c>
       <c r="G9">
-        <v>520.7222222222224</v>
+        <v>333.33333333333343</v>
       </c>
       <c r="H9">
-        <v>70.083333333333343</v>
+        <v>39.44444444444445</v>
       </c>
       <c r="I9">
-        <v>4.6589655999996467</v>
+        <v>5.2023584999988088</v>
       </c>
       <c r="J9">
-        <v>2.707709999231156E-2</v>
+        <v>3.1438799996976741E-2</v>
       </c>
       <c r="K9">
-        <v>4.6860426999919582</v>
-      </c>
-      <c r="M9">
-        <f t="shared" si="0"/>
-        <v>171.01388888888914</v>
-      </c>
-      <c r="N9">
-        <f t="shared" si="1"/>
-        <v>349.70833333333326</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+        <v>5.2337972999957856</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11">
       <c r="A10">
         <v>70000</v>
       </c>
@@ -2396,39 +1772,31 @@
         <v>700</v>
       </c>
       <c r="D10">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="E10">
         <v>9</v>
       </c>
       <c r="F10">
-        <v>288.05555555555537</v>
+        <v>241.7777777777778</v>
       </c>
       <c r="G10">
-        <v>288.05555555555537</v>
+        <v>228.2777777777778</v>
       </c>
       <c r="H10">
-        <v>42.694444444444443</v>
+        <v>35.277777777777771</v>
       </c>
       <c r="I10">
-        <v>4.5848924000019906</v>
+        <v>4.8761056999937864</v>
       </c>
       <c r="J10">
-        <v>2.5847099997918122E-2</v>
+        <v>5.001149998861365E-2</v>
       </c>
       <c r="K10">
-        <v>4.6107394999999087</v>
-      </c>
-      <c r="M10">
-        <f t="shared" si="0"/>
-        <v>61.652777777777885</v>
-      </c>
-      <c r="N10">
-        <f t="shared" si="1"/>
-        <v>349.70833333333326</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+        <v>4.9261171999824001</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11">
       <c r="A11">
         <v>70000</v>
       </c>
@@ -2439,39 +1807,31 @@
         <v>700</v>
       </c>
       <c r="D11">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="E11">
         <v>10</v>
       </c>
       <c r="F11">
-        <v>519.27777777777783</v>
+        <v>375.08333333333331</v>
       </c>
       <c r="G11">
-        <v>519.27777777777783</v>
+        <v>375.08333333333331</v>
       </c>
       <c r="H11">
-        <v>62.916666666666671</v>
+        <v>49.472222222222221</v>
       </c>
       <c r="I11">
-        <v>4.442677700004424</v>
+        <v>5.1273934999917401</v>
       </c>
       <c r="J11">
-        <v>2.6426300013554279E-2</v>
+        <v>3.8930399998207577E-2</v>
       </c>
       <c r="K11">
-        <v>4.4691040000179783</v>
-      </c>
-      <c r="M11">
-        <f t="shared" si="0"/>
-        <v>169.56944444444457</v>
-      </c>
-      <c r="N11">
-        <f t="shared" si="1"/>
-        <v>349.70833333333326</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+        <v>5.1663238999899477</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11">
       <c r="A12">
         <v>70000</v>
       </c>
@@ -2482,39 +1842,31 @@
         <v>700</v>
       </c>
       <c r="D12">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="E12">
         <v>11</v>
       </c>
       <c r="F12">
-        <v>329.5833333333332</v>
+        <v>168.5</v>
       </c>
       <c r="G12">
-        <v>329.5833333333332</v>
+        <v>168.5</v>
       </c>
       <c r="H12">
-        <v>49.416666666666643</v>
+        <v>22.833333333333329</v>
       </c>
       <c r="I12">
-        <v>4.6914169000083348</v>
+        <v>4.8768200000049546</v>
       </c>
       <c r="J12">
-        <v>2.5309799995739009E-2</v>
+        <v>2.7552699990337711E-2</v>
       </c>
       <c r="K12">
-        <v>4.7167267000040738</v>
-      </c>
-      <c r="M12">
-        <f t="shared" si="0"/>
-        <v>20.125000000000057</v>
-      </c>
-      <c r="N12">
-        <f t="shared" si="1"/>
-        <v>349.70833333333326</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+        <v>4.9043726999952924</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11">
       <c r="A13">
         <v>70000</v>
       </c>
@@ -2525,39 +1877,31 @@
         <v>700</v>
       </c>
       <c r="D13">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="E13">
         <v>12</v>
       </c>
       <c r="F13">
-        <v>420.27777777777771</v>
+        <v>279.69444444444429</v>
       </c>
       <c r="G13">
-        <v>420.27777777777771</v>
+        <v>279.69444444444429</v>
       </c>
       <c r="H13">
-        <v>47.583333333333329</v>
+        <v>42.027777777777757</v>
       </c>
       <c r="I13">
-        <v>4.6121975999994902</v>
+        <v>4.8244544999906793</v>
       </c>
       <c r="J13">
-        <v>2.5985000000218861E-2</v>
+        <v>2.8693000000203028E-2</v>
       </c>
       <c r="K13">
-        <v>4.6381825999997091</v>
-      </c>
-      <c r="M13">
-        <f t="shared" si="0"/>
-        <v>70.569444444444457</v>
-      </c>
-      <c r="N13">
-        <f t="shared" si="1"/>
-        <v>349.70833333333326</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+        <v>4.8531474999908824</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11">
       <c r="A14">
         <v>70000</v>
       </c>
@@ -2568,39 +1912,31 @@
         <v>700</v>
       </c>
       <c r="D14">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="E14">
         <v>13</v>
       </c>
       <c r="F14">
-        <v>224.5</v>
+        <v>282.83333333333343</v>
       </c>
       <c r="G14">
-        <v>206.33333333333329</v>
+        <v>282.83333333333343</v>
       </c>
       <c r="H14">
-        <v>29.055555555555561</v>
+        <v>44.916666666666679</v>
       </c>
       <c r="I14">
-        <v>4.6470414999930654</v>
+        <v>4.7672271000046749</v>
       </c>
       <c r="J14">
-        <v>7.4611599993659183E-2</v>
+        <v>2.617179999651853E-2</v>
       </c>
       <c r="K14">
-        <v>4.7216530999867254</v>
-      </c>
-      <c r="M14">
-        <f t="shared" si="0"/>
-        <v>143.37499999999997</v>
-      </c>
-      <c r="N14">
-        <f t="shared" si="1"/>
-        <v>349.70833333333326</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+        <v>4.7933989000011934</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11">
       <c r="A15">
         <v>70000</v>
       </c>
@@ -2611,39 +1947,31 @@
         <v>700</v>
       </c>
       <c r="D15">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="E15">
         <v>14</v>
       </c>
       <c r="F15">
-        <v>255.6666666666668</v>
+        <v>267.94444444444451</v>
       </c>
       <c r="G15">
-        <v>252.1666666666668</v>
+        <v>267.94444444444451</v>
       </c>
       <c r="H15">
-        <v>40.000000000000007</v>
+        <v>40.027777777777779</v>
       </c>
       <c r="I15">
-        <v>4.4126542000012714</v>
+        <v>6.4639587999990908</v>
       </c>
       <c r="J15">
-        <v>4.8726399996667169E-2</v>
+        <v>3.2498000000487082E-2</v>
       </c>
       <c r="K15">
-        <v>4.4613805999979377</v>
-      </c>
-      <c r="M15">
-        <f t="shared" si="0"/>
-        <v>97.541666666666458</v>
-      </c>
-      <c r="N15">
-        <f t="shared" si="1"/>
-        <v>349.70833333333326</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
+        <v>6.4964567999995779</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11">
       <c r="A16">
         <v>70000</v>
       </c>
@@ -2654,39 +1982,31 @@
         <v>700</v>
       </c>
       <c r="D16">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="E16">
         <v>15</v>
       </c>
       <c r="F16">
-        <v>411.52777777777783</v>
+        <v>254.02777777777769</v>
       </c>
       <c r="G16">
-        <v>282.80555555555549</v>
+        <v>254.02777777777769</v>
       </c>
       <c r="H16">
-        <v>34.805555555555557</v>
+        <v>40.194444444444443</v>
       </c>
       <c r="I16">
-        <v>4.670396499990602</v>
+        <v>4.700940199996694</v>
       </c>
       <c r="J16">
-        <v>9.1184300006716512E-2</v>
+        <v>2.7870699996128678E-2</v>
       </c>
       <c r="K16">
-        <v>4.7615807999973194</v>
-      </c>
-      <c r="M16">
-        <f t="shared" si="0"/>
-        <v>66.902777777777771</v>
-      </c>
-      <c r="N16">
-        <f t="shared" si="1"/>
-        <v>349.70833333333326</v>
-      </c>
-    </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
+        <v>4.7288108999928227</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11">
       <c r="A17">
         <v>70000</v>
       </c>
@@ -2697,39 +2017,31 @@
         <v>700</v>
       </c>
       <c r="D17">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="E17">
         <v>16</v>
       </c>
       <c r="F17">
-        <v>292.8888888888888</v>
+        <v>612.91666666666652</v>
       </c>
       <c r="G17">
-        <v>292.8888888888888</v>
+        <v>612.91666666666652</v>
       </c>
       <c r="H17">
-        <v>33.6111111111111</v>
+        <v>83.166666666666643</v>
       </c>
       <c r="I17">
-        <v>4.7255049999948824</v>
+        <v>5.1174462999915704</v>
       </c>
       <c r="J17">
-        <v>2.6741599998786111E-2</v>
+        <v>2.714210000704043E-2</v>
       </c>
       <c r="K17">
-        <v>4.7522465999936676</v>
-      </c>
-      <c r="M17">
-        <f t="shared" si="0"/>
-        <v>56.819444444444457</v>
-      </c>
-      <c r="N17">
-        <f t="shared" si="1"/>
-        <v>349.70833333333326</v>
-      </c>
-    </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
+        <v>5.1445883999986108</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11">
       <c r="A18">
         <v>70000</v>
       </c>
@@ -2740,39 +2052,31 @@
         <v>700</v>
       </c>
       <c r="D18">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="E18">
         <v>17</v>
       </c>
       <c r="F18">
-        <v>389.77777777777811</v>
+        <v>482.66666666666669</v>
       </c>
       <c r="G18">
-        <v>389.77777777777811</v>
+        <v>482.66666666666669</v>
       </c>
       <c r="H18">
-        <v>57.750000000000028</v>
+        <v>61.250000000000007</v>
       </c>
       <c r="I18">
-        <v>4.5051876999932574</v>
+        <v>4.7484903000004124</v>
       </c>
       <c r="J18">
-        <v>2.740419999463484E-2</v>
+        <v>2.6184000002103861E-2</v>
       </c>
       <c r="K18">
-        <v>4.5325918999878922</v>
-      </c>
-      <c r="M18">
-        <f t="shared" si="0"/>
-        <v>40.069444444444855</v>
-      </c>
-      <c r="N18">
-        <f t="shared" si="1"/>
-        <v>349.70833333333326</v>
-      </c>
-    </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
+        <v>4.7746743000025162</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11">
       <c r="A19">
         <v>70000</v>
       </c>
@@ -2783,39 +2087,31 @@
         <v>700</v>
       </c>
       <c r="D19">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="E19">
         <v>18</v>
       </c>
       <c r="F19">
-        <v>253.25</v>
+        <v>328.58333333333343</v>
       </c>
       <c r="G19">
-        <v>253.25</v>
+        <v>328.58333333333343</v>
       </c>
       <c r="H19">
-        <v>39.416666666666657</v>
+        <v>48.194444444444457</v>
       </c>
       <c r="I19">
-        <v>4.521092499999213</v>
+        <v>4.8462811000063084</v>
       </c>
       <c r="J19">
-        <v>2.4690299993380901E-2</v>
+        <v>2.6019900004030209E-2</v>
       </c>
       <c r="K19">
-        <v>4.5457827999925939</v>
-      </c>
-      <c r="M19">
-        <f t="shared" si="0"/>
-        <v>96.458333333333258</v>
-      </c>
-      <c r="N19">
-        <f t="shared" si="1"/>
-        <v>349.70833333333326</v>
-      </c>
-    </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
+        <v>4.8723010000103386</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11">
       <c r="A20">
         <v>70000</v>
       </c>
@@ -2826,39 +2122,31 @@
         <v>700</v>
       </c>
       <c r="D20">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="E20">
         <v>19</v>
       </c>
       <c r="F20">
-        <v>298.49999999999989</v>
+        <v>268.47222222222229</v>
       </c>
       <c r="G20">
-        <v>298.49999999999989</v>
+        <v>268.47222222222229</v>
       </c>
       <c r="H20">
-        <v>43.41666666666665</v>
+        <v>42.527777777777779</v>
       </c>
       <c r="I20">
-        <v>4.4804460999876028</v>
+        <v>4.7808438000065507</v>
       </c>
       <c r="J20">
-        <v>2.4080200004391369E-2</v>
+        <v>2.7148199995281171E-2</v>
       </c>
       <c r="K20">
-        <v>4.5045262999919942</v>
-      </c>
-      <c r="M20">
-        <f t="shared" si="0"/>
-        <v>51.208333333333371</v>
-      </c>
-      <c r="N20">
-        <f t="shared" si="1"/>
-        <v>349.70833333333326</v>
-      </c>
-    </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
+        <v>4.8079920000018319</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11">
       <c r="A21">
         <v>70000</v>
       </c>
@@ -2869,39 +2157,31 @@
         <v>700</v>
       </c>
       <c r="D21">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="E21">
         <v>20</v>
       </c>
       <c r="F21">
-        <v>379.49999999999989</v>
+        <v>522.5</v>
       </c>
       <c r="G21">
-        <v>379.49999999999989</v>
+        <v>522.5</v>
       </c>
       <c r="H21">
-        <v>54.305555555555543</v>
+        <v>70.194444444444443</v>
       </c>
       <c r="I21">
-        <v>4.5414391999947838</v>
+        <v>5.3990511000010883</v>
       </c>
       <c r="J21">
-        <v>2.7172000001883131E-2</v>
+        <v>2.875179999682587E-2</v>
       </c>
       <c r="K21">
-        <v>4.568611199996667</v>
-      </c>
-      <c r="M21">
-        <f t="shared" si="0"/>
-        <v>29.791666666666629</v>
-      </c>
-      <c r="N21">
-        <f t="shared" si="1"/>
-        <v>349.70833333333326</v>
-      </c>
-    </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
+        <v>5.4278028999979142</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11">
       <c r="A22">
         <v>70000</v>
       </c>
@@ -2912,39 +2192,31 @@
         <v>700</v>
       </c>
       <c r="D22">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="E22">
         <v>21</v>
       </c>
       <c r="F22">
-        <v>560.58333333333337</v>
+        <v>333.61111111111109</v>
       </c>
       <c r="G22">
-        <v>560.58333333333337</v>
+        <v>333.61111111111109</v>
       </c>
       <c r="H22">
-        <v>75.666666666666671</v>
+        <v>48.611111111111107</v>
       </c>
       <c r="I22">
-        <v>4.6203573999955552</v>
+        <v>5.4854661999997916</v>
       </c>
       <c r="J22">
-        <v>2.602039999328554E-2</v>
+        <v>2.8335599999991249E-2</v>
       </c>
       <c r="K22">
-        <v>4.6463777999888407</v>
-      </c>
-      <c r="M22">
-        <f t="shared" si="0"/>
-        <v>210.87500000000011</v>
-      </c>
-      <c r="N22">
-        <f t="shared" si="1"/>
-        <v>349.70833333333326</v>
-      </c>
-    </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
+        <v>5.5138017999997828</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11">
       <c r="A23">
         <v>70000</v>
       </c>
@@ -2955,39 +2227,31 @@
         <v>700</v>
       </c>
       <c r="D23">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="E23">
         <v>22</v>
       </c>
       <c r="F23">
-        <v>316.55555555555571</v>
+        <v>390.6111111111112</v>
       </c>
       <c r="G23">
-        <v>316.55555555555571</v>
+        <v>390.6111111111112</v>
       </c>
       <c r="H23">
-        <v>46.722222222222229</v>
+        <v>55.361111111111107</v>
       </c>
       <c r="I23">
-        <v>4.4373579999955837</v>
+        <v>4.9465278999996372</v>
       </c>
       <c r="J23">
-        <v>2.4686500008101579E-2</v>
+        <v>2.485099999466911E-2</v>
       </c>
       <c r="K23">
-        <v>4.4620445000036852</v>
-      </c>
-      <c r="M23">
-        <f t="shared" si="0"/>
-        <v>33.152777777777544</v>
-      </c>
-      <c r="N23">
-        <f t="shared" si="1"/>
-        <v>349.70833333333326</v>
-      </c>
-    </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
+        <v>4.9713788999943063</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11">
       <c r="A24">
         <v>70000</v>
       </c>
@@ -2998,39 +2262,31 @@
         <v>700</v>
       </c>
       <c r="D24">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="E24">
         <v>23</v>
       </c>
       <c r="F24">
-        <v>441.6111111111112</v>
+        <v>192.4444444444446</v>
       </c>
       <c r="G24">
-        <v>419.6111111111112</v>
+        <v>192.4444444444446</v>
       </c>
       <c r="H24">
-        <v>58.000000000000007</v>
+        <v>30.444444444444461</v>
       </c>
       <c r="I24">
-        <v>4.5276949000108289</v>
+        <v>4.9659979999996722</v>
       </c>
       <c r="J24">
-        <v>4.9588200010475703E-2</v>
+        <v>2.638670000305865E-2</v>
       </c>
       <c r="K24">
-        <v>4.5772831000213046</v>
-      </c>
-      <c r="M24">
-        <f t="shared" si="0"/>
-        <v>69.902777777777942</v>
-      </c>
-      <c r="N24">
-        <f t="shared" si="1"/>
-        <v>349.70833333333326</v>
-      </c>
-    </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
+        <v>4.9923847000027308</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11">
       <c r="A25">
         <v>70000</v>
       </c>
@@ -3041,39 +2297,31 @@
         <v>700</v>
       </c>
       <c r="D25">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="E25">
         <v>24</v>
       </c>
       <c r="F25">
-        <v>282.33333333333343</v>
+        <v>246.7777777777776</v>
       </c>
       <c r="G25">
-        <v>282.33333333333343</v>
+        <v>246.7777777777776</v>
       </c>
       <c r="H25">
-        <v>31.250000000000011</v>
+        <v>38.166666666666643</v>
       </c>
       <c r="I25">
-        <v>4.5951457000046503</v>
+        <v>5.2402036999992561</v>
       </c>
       <c r="J25">
-        <v>2.4164899994502779E-2</v>
+        <v>2.7915800004848279E-2</v>
       </c>
       <c r="K25">
-        <v>4.6193105999991531</v>
-      </c>
-      <c r="M25">
-        <f t="shared" si="0"/>
-        <v>67.374999999999829</v>
-      </c>
-      <c r="N25">
-        <f t="shared" si="1"/>
-        <v>349.70833333333326</v>
-      </c>
-    </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
+        <v>5.2681195000041043</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11">
       <c r="A26">
         <v>70000</v>
       </c>
@@ -3084,39 +2332,31 @@
         <v>700</v>
       </c>
       <c r="D26">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="E26">
         <v>25</v>
       </c>
       <c r="F26">
-        <v>365.99999999999989</v>
+        <v>461.94444444444451</v>
       </c>
       <c r="G26">
-        <v>353.99999999999989</v>
+        <v>461.94444444444451</v>
       </c>
       <c r="H26">
-        <v>50.583333333333321</v>
+        <v>68.166666666666671</v>
       </c>
       <c r="I26">
-        <v>4.553966199993738</v>
+        <v>5.6907558000093559</v>
       </c>
       <c r="J26">
-        <v>4.7483100002864383E-2</v>
+        <v>2.5732899986905981E-2</v>
       </c>
       <c r="K26">
-        <v>4.6014492999966023</v>
-      </c>
-      <c r="M26">
-        <f t="shared" si="0"/>
-        <v>4.2916666666666288</v>
-      </c>
-      <c r="N26">
-        <f t="shared" si="1"/>
-        <v>349.70833333333326</v>
-      </c>
-    </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
+        <v>5.7164886999962619</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11">
       <c r="A27">
         <v>70000</v>
       </c>
@@ -3127,39 +2367,31 @@
         <v>700</v>
       </c>
       <c r="D27">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="E27">
         <v>26</v>
       </c>
       <c r="F27">
-        <v>288.38888888888891</v>
+        <v>378</v>
       </c>
       <c r="G27">
-        <v>288.38888888888891</v>
+        <v>378</v>
       </c>
       <c r="H27">
-        <v>42.527777777777779</v>
+        <v>51.75</v>
       </c>
       <c r="I27">
-        <v>4.4120253000000957</v>
+        <v>4.9171762000041781</v>
       </c>
       <c r="J27">
-        <v>2.447530000063125E-2</v>
+        <v>2.6721100002760071E-2</v>
       </c>
       <c r="K27">
-        <v>4.436500600000727</v>
-      </c>
-      <c r="M27">
-        <f t="shared" si="0"/>
-        <v>61.319444444444343</v>
-      </c>
-      <c r="N27">
-        <f t="shared" si="1"/>
-        <v>349.70833333333326</v>
-      </c>
-    </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
+        <v>4.9438973000069382</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11">
       <c r="A28">
         <v>70000</v>
       </c>
@@ -3170,39 +2402,31 @@
         <v>700</v>
       </c>
       <c r="D28">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="E28">
         <v>27</v>
       </c>
       <c r="F28">
-        <v>294.50000000000011</v>
+        <v>350.83333333333309</v>
       </c>
       <c r="G28">
-        <v>294.50000000000011</v>
+        <v>334.94444444444417</v>
       </c>
       <c r="H28">
-        <v>42.888888888888893</v>
+        <v>49.694444444444422</v>
       </c>
       <c r="I28">
-        <v>4.704649999999674</v>
+        <v>4.6372984000045108</v>
       </c>
       <c r="J28">
-        <v>3.6172899999655783E-2</v>
+        <v>4.9446699995314702E-2</v>
       </c>
       <c r="K28">
-        <v>4.7408228999993298</v>
-      </c>
-      <c r="M28">
-        <f t="shared" si="0"/>
-        <v>55.208333333333144</v>
-      </c>
-      <c r="N28">
-        <f t="shared" si="1"/>
-        <v>349.70833333333326</v>
-      </c>
-    </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
+        <v>4.6867450999998246</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11">
       <c r="A29">
         <v>70000</v>
       </c>
@@ -3213,39 +2437,31 @@
         <v>700</v>
       </c>
       <c r="D29">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="E29">
         <v>28</v>
       </c>
       <c r="F29">
-        <v>394.88888888888869</v>
+        <v>315.8333333333336</v>
       </c>
       <c r="G29">
-        <v>394.88888888888869</v>
+        <v>315.8333333333336</v>
       </c>
       <c r="H29">
-        <v>58.166666666666643</v>
+        <v>43.527777777777807</v>
       </c>
       <c r="I29">
-        <v>4.7666188999864971</v>
+        <v>4.6937429999961751</v>
       </c>
       <c r="J29">
-        <v>2.6740700006484989E-2</v>
+        <v>2.4894799993489869E-2</v>
       </c>
       <c r="K29">
-        <v>4.7933595999929821</v>
-      </c>
-      <c r="M29">
-        <f t="shared" si="0"/>
-        <v>45.180555555555429</v>
-      </c>
-      <c r="N29">
-        <f t="shared" si="1"/>
-        <v>349.70833333333326</v>
-      </c>
-    </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
+        <v>4.7186377999896649</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11">
       <c r="A30">
         <v>70000</v>
       </c>
@@ -3256,39 +2472,31 @@
         <v>700</v>
       </c>
       <c r="D30">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="E30">
         <v>29</v>
       </c>
       <c r="F30">
-        <v>458.91666666666652</v>
+        <v>358.02777777777749</v>
       </c>
       <c r="G30">
-        <v>458.91666666666652</v>
+        <v>358.02777777777749</v>
       </c>
       <c r="H30">
-        <v>59.999999999999972</v>
+        <v>54.5833333333333</v>
       </c>
       <c r="I30">
-        <v>4.5738898000126937</v>
+        <v>4.6634412999992492</v>
       </c>
       <c r="J30">
-        <v>2.6802000007592142E-2</v>
+        <v>3.0098599992925301E-2</v>
       </c>
       <c r="K30">
-        <v>4.6006918000202859</v>
-      </c>
-      <c r="M30">
-        <f t="shared" si="0"/>
-        <v>109.20833333333326</v>
-      </c>
-      <c r="N30">
-        <f t="shared" si="1"/>
-        <v>349.70833333333326</v>
-      </c>
-    </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.25">
+        <v>4.6935398999921736</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11">
       <c r="A31">
         <v>70000</v>
       </c>
@@ -3299,39 +2507,31 @@
         <v>700</v>
       </c>
       <c r="D31">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="E31">
         <v>30</v>
       </c>
       <c r="F31">
-        <v>393</v>
+        <v>252.61111111111109</v>
       </c>
       <c r="G31">
-        <v>393</v>
+        <v>252.61111111111109</v>
       </c>
       <c r="H31">
-        <v>54.916666666666671</v>
+        <v>37.333333333333329</v>
       </c>
       <c r="I31">
-        <v>4.5056306000042241</v>
+        <v>4.8996674999943934</v>
       </c>
       <c r="J31">
-        <v>2.8951399988727641E-2</v>
+        <v>2.6194199992460199E-2</v>
       </c>
       <c r="K31">
-        <v>4.5345819999929518</v>
-      </c>
-      <c r="M31">
-        <f t="shared" si="0"/>
-        <v>43.291666666666742</v>
-      </c>
-      <c r="N31">
-        <f t="shared" si="1"/>
-        <v>349.70833333333326</v>
-      </c>
-    </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.25">
+        <v>4.9258616999868536</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11">
       <c r="A32">
         <v>70000</v>
       </c>
@@ -3342,39 +2542,31 @@
         <v>700</v>
       </c>
       <c r="D32">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="E32">
         <v>31</v>
       </c>
       <c r="F32">
-        <v>426.44444444444451</v>
+        <v>295.16666666666691</v>
       </c>
       <c r="G32">
-        <v>426.44444444444451</v>
+        <v>295.16666666666691</v>
       </c>
       <c r="H32">
-        <v>58.638888888888893</v>
+        <v>43.055555555555571</v>
       </c>
       <c r="I32">
-        <v>4.5530281999963336</v>
+        <v>4.6228814999922179</v>
       </c>
       <c r="J32">
-        <v>2.2279299999354411E-2</v>
+        <v>2.2193800003151409E-2</v>
       </c>
       <c r="K32">
-        <v>4.575307499995688</v>
-      </c>
-      <c r="M32">
-        <f t="shared" si="0"/>
-        <v>76.736111111111256</v>
-      </c>
-      <c r="N32">
-        <f t="shared" si="1"/>
-        <v>349.70833333333326</v>
-      </c>
-    </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.25">
+        <v>4.6450752999953693</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11">
       <c r="A33">
         <v>70000</v>
       </c>
@@ -3385,39 +2577,31 @@
         <v>700</v>
       </c>
       <c r="D33">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="E33">
         <v>32</v>
       </c>
       <c r="F33">
-        <v>144</v>
+        <v>290.58333333333331</v>
       </c>
       <c r="G33">
-        <v>144</v>
+        <v>290.58333333333331</v>
       </c>
       <c r="H33">
-        <v>23</v>
+        <v>45.472222222222207</v>
       </c>
       <c r="I33">
-        <v>4.3014274000015584</v>
+        <v>4.576222300005611</v>
       </c>
       <c r="J33">
-        <v>2.216429999680258E-2</v>
+        <v>2.5649699993664399E-2</v>
       </c>
       <c r="K33">
-        <v>4.3235916999983601</v>
-      </c>
-      <c r="M33">
-        <f t="shared" si="0"/>
-        <v>205.70833333333326</v>
-      </c>
-      <c r="N33">
-        <f t="shared" si="1"/>
-        <v>349.70833333333326</v>
-      </c>
-    </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.25">
+        <v>4.6018719999992754</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11">
       <c r="A34">
         <v>70000</v>
       </c>
@@ -3428,39 +2612,31 @@
         <v>700</v>
       </c>
       <c r="D34">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="E34">
         <v>33</v>
       </c>
       <c r="F34">
-        <v>359.97222222222229</v>
+        <v>272.94444444444463</v>
       </c>
       <c r="G34">
-        <v>359.97222222222229</v>
+        <v>272.94444444444463</v>
       </c>
       <c r="H34">
-        <v>51.111111111111128</v>
+        <v>38.444444444444457</v>
       </c>
       <c r="I34">
-        <v>4.3094290000008186</v>
+        <v>4.5383169999986421</v>
       </c>
       <c r="J34">
-        <v>2.2420799999963489E-2</v>
+        <v>2.740949999133591E-2</v>
       </c>
       <c r="K34">
-        <v>4.3318498000007821</v>
-      </c>
-      <c r="M34">
-        <f t="shared" si="0"/>
-        <v>10.263888888889028</v>
-      </c>
-      <c r="N34">
-        <f t="shared" si="1"/>
-        <v>349.70833333333326</v>
-      </c>
-    </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.25">
+        <v>4.565726499989978</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11">
       <c r="A35">
         <v>70000</v>
       </c>
@@ -3471,39 +2647,31 @@
         <v>700</v>
       </c>
       <c r="D35">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="E35">
         <v>34</v>
       </c>
       <c r="F35">
-        <v>471.50000000000011</v>
+        <v>376.66666666666657</v>
       </c>
       <c r="G35">
-        <v>471.50000000000011</v>
+        <v>376.66666666666657</v>
       </c>
       <c r="H35">
-        <v>50.277777777777793</v>
+        <v>49.749999999999993</v>
       </c>
       <c r="I35">
-        <v>4.3737662000057753</v>
+        <v>4.519452900000033</v>
       </c>
       <c r="J35">
-        <v>2.2894800000358369E-2</v>
+        <v>2.232530000037514E-2</v>
       </c>
       <c r="K35">
-        <v>4.3966610000061337</v>
-      </c>
-      <c r="M35">
-        <f t="shared" si="0"/>
-        <v>121.79166666666686</v>
-      </c>
-      <c r="N35">
-        <f t="shared" si="1"/>
-        <v>349.70833333333326</v>
-      </c>
-    </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.25">
+        <v>4.5417782000004081</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11">
       <c r="A36">
         <v>70000</v>
       </c>
@@ -3514,39 +2682,31 @@
         <v>700</v>
       </c>
       <c r="D36">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="E36">
         <v>35</v>
       </c>
       <c r="F36">
-        <v>504.24999999999977</v>
+        <v>182.52777777777791</v>
       </c>
       <c r="G36">
-        <v>504.24999999999977</v>
+        <v>178.7777777777778</v>
       </c>
       <c r="H36">
-        <v>73.416666666666657</v>
+        <v>21.833333333333339</v>
       </c>
       <c r="I36">
-        <v>4.260836700006621</v>
+        <v>4.6667966000095484</v>
       </c>
       <c r="J36">
-        <v>2.1456399990711361E-2</v>
+        <v>4.6548099999199621E-2</v>
       </c>
       <c r="K36">
-        <v>4.2822930999973323</v>
-      </c>
-      <c r="M36">
-        <f t="shared" si="0"/>
-        <v>154.54166666666652</v>
-      </c>
-      <c r="N36">
-        <f t="shared" si="1"/>
-        <v>349.70833333333326</v>
-      </c>
-    </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.25">
+        <v>4.7133447000087472</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11">
       <c r="A37">
         <v>70000</v>
       </c>
@@ -3557,39 +2717,31 @@
         <v>700</v>
       </c>
       <c r="D37">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="E37">
         <v>36</v>
       </c>
       <c r="F37">
-        <v>305.94444444444417</v>
+        <v>310.77777777777771</v>
       </c>
       <c r="G37">
-        <v>305.94444444444417</v>
+        <v>308.55555555555537</v>
       </c>
       <c r="H37">
-        <v>31.833333333333311</v>
+        <v>37.833333333333307</v>
       </c>
       <c r="I37">
-        <v>4.3506750999949872</v>
+        <v>4.3758331999997608</v>
       </c>
       <c r="J37">
-        <v>2.2731899996870201E-2</v>
+        <v>4.4139000005088747E-2</v>
       </c>
       <c r="K37">
-        <v>4.3734069999918566</v>
-      </c>
-      <c r="M37">
-        <f t="shared" si="0"/>
-        <v>43.763888888889085</v>
-      </c>
-      <c r="N37">
-        <f t="shared" si="1"/>
-        <v>349.70833333333326</v>
-      </c>
-    </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.25">
+        <v>4.4199722000048496</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11">
       <c r="A38">
         <v>70000</v>
       </c>
@@ -3600,39 +2752,31 @@
         <v>700</v>
       </c>
       <c r="D38">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="E38">
         <v>37</v>
       </c>
       <c r="F38">
-        <v>293.00000000000011</v>
+        <v>313.27777777777783</v>
       </c>
       <c r="G38">
-        <v>273.83333333333331</v>
+        <v>313.27777777777783</v>
       </c>
       <c r="H38">
-        <v>41.249999999999993</v>
+        <v>46.305555555555557</v>
       </c>
       <c r="I38">
-        <v>4.3794996000069659</v>
+        <v>4.4544587999989744</v>
       </c>
       <c r="J38">
-        <v>6.3699599995743483E-2</v>
+        <v>2.4106600001687181E-2</v>
       </c>
       <c r="K38">
-        <v>4.4431992000027094</v>
-      </c>
-      <c r="M38">
-        <f t="shared" si="0"/>
-        <v>75.874999999999943</v>
-      </c>
-      <c r="N38">
-        <f t="shared" si="1"/>
-        <v>349.70833333333326</v>
-      </c>
-    </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.25">
+        <v>4.4785654000006616</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11">
       <c r="A39">
         <v>70000</v>
       </c>
@@ -3643,39 +2787,31 @@
         <v>700</v>
       </c>
       <c r="D39">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="E39">
         <v>38</v>
       </c>
       <c r="F39">
-        <v>501.94444444444468</v>
+        <v>395.88888888888869</v>
       </c>
       <c r="G39">
-        <v>501.94444444444468</v>
+        <v>395.88888888888869</v>
       </c>
       <c r="H39">
-        <v>53.194444444444457</v>
+        <v>55.9722222222222</v>
       </c>
       <c r="I39">
-        <v>4.3372454999916954</v>
+        <v>4.4198136000049999</v>
       </c>
       <c r="J39">
-        <v>2.1949699992546812E-2</v>
+        <v>2.3183800003607761E-2</v>
       </c>
       <c r="K39">
-        <v>4.3591951999842422</v>
-      </c>
-      <c r="M39">
-        <f t="shared" si="0"/>
-        <v>152.23611111111143</v>
-      </c>
-      <c r="N39">
-        <f t="shared" si="1"/>
-        <v>349.70833333333326</v>
-      </c>
-    </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.25">
+        <v>4.4429974000086077</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11">
       <c r="A40">
         <v>70000</v>
       </c>
@@ -3686,39 +2822,31 @@
         <v>700</v>
       </c>
       <c r="D40">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="E40">
         <v>39</v>
       </c>
       <c r="F40">
-        <v>267.94444444444429</v>
+        <v>314.77777777777783</v>
       </c>
       <c r="G40">
-        <v>267.94444444444429</v>
+        <v>314.77777777777783</v>
       </c>
       <c r="H40">
-        <v>40.027777777777757</v>
+        <v>46.166666666666671</v>
       </c>
       <c r="I40">
-        <v>4.2827115000109188</v>
+        <v>4.3814789000025476</v>
       </c>
       <c r="J40">
-        <v>2.2018800009391271E-2</v>
+        <v>2.708269999129698E-2</v>
       </c>
       <c r="K40">
-        <v>4.3047303000203101</v>
-      </c>
-      <c r="M40">
-        <f t="shared" si="0"/>
-        <v>81.763888888888971</v>
-      </c>
-      <c r="N40">
-        <f t="shared" si="1"/>
-        <v>349.70833333333326</v>
-      </c>
-    </row>
-    <row r="41" spans="1:14" x14ac:dyDescent="0.25">
+        <v>4.4085615999938446</v>
+      </c>
+    </row>
+    <row r="41" spans="1:11">
       <c r="A41">
         <v>70000</v>
       </c>
@@ -3729,39 +2857,31 @@
         <v>700</v>
       </c>
       <c r="D41">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="E41">
         <v>40</v>
       </c>
       <c r="F41">
-        <v>398.58333333333331</v>
+        <v>444.77777777777783</v>
       </c>
       <c r="G41">
-        <v>398.58333333333331</v>
+        <v>444.77777777777783</v>
       </c>
       <c r="H41">
-        <v>59.80555555555555</v>
+        <v>63.916666666666671</v>
       </c>
       <c r="I41">
-        <v>4.2708839000115404</v>
+        <v>4.5326510000013513</v>
       </c>
       <c r="J41">
-        <v>2.228560000366997E-2</v>
+        <v>2.5055799997062419E-2</v>
       </c>
       <c r="K41">
-        <v>4.2931695000152104</v>
-      </c>
-      <c r="M41">
-        <f t="shared" si="0"/>
-        <v>48.875000000000057</v>
-      </c>
-      <c r="N41">
-        <f t="shared" si="1"/>
-        <v>349.70833333333326</v>
-      </c>
-    </row>
-    <row r="42" spans="1:14" x14ac:dyDescent="0.25">
+        <v>4.5577067999984138</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11">
       <c r="A42">
         <v>70000</v>
       </c>
@@ -3772,39 +2892,31 @@
         <v>700</v>
       </c>
       <c r="D42">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="E42">
         <v>41</v>
       </c>
       <c r="F42">
-        <v>337.00000000000011</v>
+        <v>623.00000000000011</v>
       </c>
       <c r="G42">
-        <v>337.00000000000011</v>
+        <v>623.00000000000011</v>
       </c>
       <c r="H42">
-        <v>49.527777777777779</v>
+        <v>75.277777777777786</v>
       </c>
       <c r="I42">
-        <v>4.3617032000038307</v>
+        <v>4.4393082000024151</v>
       </c>
       <c r="J42">
-        <v>2.177009999286383E-2</v>
+        <v>2.336209999339189E-2</v>
       </c>
       <c r="K42">
-        <v>4.3834732999966954</v>
-      </c>
-      <c r="M42">
-        <f t="shared" si="0"/>
-        <v>12.708333333333144</v>
-      </c>
-      <c r="N42">
-        <f t="shared" si="1"/>
-        <v>349.70833333333326</v>
-      </c>
-    </row>
-    <row r="43" spans="1:14" x14ac:dyDescent="0.25">
+        <v>4.462670299995807</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11">
       <c r="A43">
         <v>70000</v>
       </c>
@@ -3815,39 +2927,31 @@
         <v>700</v>
       </c>
       <c r="D43">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="E43">
         <v>42</v>
       </c>
       <c r="F43">
-        <v>267.25</v>
+        <v>349.5</v>
       </c>
       <c r="G43">
-        <v>267.25</v>
+        <v>323.5</v>
       </c>
       <c r="H43">
-        <v>42.416666666666657</v>
+        <v>48</v>
       </c>
       <c r="I43">
-        <v>4.268582000004244</v>
+        <v>4.3370648999989498</v>
       </c>
       <c r="J43">
-        <v>2.195569999457803E-2</v>
+        <v>4.4185799997649162E-2</v>
       </c>
       <c r="K43">
-        <v>4.2905376999988221</v>
-      </c>
-      <c r="M43">
-        <f t="shared" si="0"/>
-        <v>82.458333333333258</v>
-      </c>
-      <c r="N43">
-        <f t="shared" si="1"/>
-        <v>349.70833333333326</v>
-      </c>
-    </row>
-    <row r="44" spans="1:14" x14ac:dyDescent="0.25">
+        <v>4.381250699996599</v>
+      </c>
+    </row>
+    <row r="44" spans="1:11">
       <c r="A44">
         <v>70000</v>
       </c>
@@ -3858,39 +2962,31 @@
         <v>700</v>
       </c>
       <c r="D44">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="E44">
         <v>43</v>
       </c>
       <c r="F44">
-        <v>460.13888888888903</v>
+        <v>208.16666666666671</v>
       </c>
       <c r="G44">
-        <v>460.13888888888903</v>
+        <v>208.16666666666671</v>
       </c>
       <c r="H44">
-        <v>64.305555555555571</v>
+        <v>29.444444444444439</v>
       </c>
       <c r="I44">
-        <v>4.3977660000091419</v>
+        <v>4.2583569999987958</v>
       </c>
       <c r="J44">
-        <v>2.214979998825584E-2</v>
+        <v>2.3328200011746961E-2</v>
       </c>
       <c r="K44">
-        <v>4.4199157999973977</v>
-      </c>
-      <c r="M44">
-        <f t="shared" si="0"/>
-        <v>110.43055555555577</v>
-      </c>
-      <c r="N44">
-        <f t="shared" si="1"/>
-        <v>349.70833333333326</v>
-      </c>
-    </row>
-    <row r="45" spans="1:14" x14ac:dyDescent="0.25">
+        <v>4.2816852000105428</v>
+      </c>
+    </row>
+    <row r="45" spans="1:11">
       <c r="A45">
         <v>70000</v>
       </c>
@@ -3901,39 +2997,31 @@
         <v>700</v>
       </c>
       <c r="D45">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="E45">
         <v>44</v>
       </c>
       <c r="F45">
-        <v>388.02777777777749</v>
+        <v>328.33333333333331</v>
       </c>
       <c r="G45">
-        <v>388.02777777777749</v>
+        <v>328.33333333333331</v>
       </c>
       <c r="H45">
-        <v>52.333333333333293</v>
+        <v>45.472222222222207</v>
       </c>
       <c r="I45">
-        <v>4.2477335000003222</v>
+        <v>4.3509132000035606</v>
       </c>
       <c r="J45">
-        <v>2.1669299996574409E-2</v>
+        <v>2.1395199990365651E-2</v>
       </c>
       <c r="K45">
-        <v>4.2694027999968966</v>
-      </c>
-      <c r="M45">
-        <f t="shared" si="0"/>
-        <v>38.31944444444423</v>
-      </c>
-      <c r="N45">
-        <f t="shared" si="1"/>
-        <v>349.70833333333326</v>
-      </c>
-    </row>
-    <row r="46" spans="1:14" x14ac:dyDescent="0.25">
+        <v>4.3723083999939263</v>
+      </c>
+    </row>
+    <row r="46" spans="1:11">
       <c r="A46">
         <v>70000</v>
       </c>
@@ -3944,39 +3032,31 @@
         <v>700</v>
       </c>
       <c r="D46">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="E46">
         <v>45</v>
       </c>
       <c r="F46">
-        <v>389.72222222222229</v>
+        <v>292.27777777777771</v>
       </c>
       <c r="G46">
-        <v>389.72222222222229</v>
+        <v>292.27777777777771</v>
       </c>
       <c r="H46">
-        <v>55.222222222222229</v>
+        <v>42.083333333333329</v>
       </c>
       <c r="I46">
-        <v>4.3080220999981984</v>
+        <v>4.3624550000095041</v>
       </c>
       <c r="J46">
-        <v>2.3524799995357171E-2</v>
+        <v>2.2986299998592589E-2</v>
       </c>
       <c r="K46">
-        <v>4.3315468999935547</v>
-      </c>
-      <c r="M46">
-        <f t="shared" si="0"/>
-        <v>40.013888888889028</v>
-      </c>
-      <c r="N46">
-        <f t="shared" si="1"/>
-        <v>349.70833333333326</v>
-      </c>
-    </row>
-    <row r="47" spans="1:14" x14ac:dyDescent="0.25">
+        <v>4.3854413000080967</v>
+      </c>
+    </row>
+    <row r="47" spans="1:11">
       <c r="A47">
         <v>70000</v>
       </c>
@@ -3987,39 +3067,31 @@
         <v>700</v>
       </c>
       <c r="D47">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="E47">
         <v>46</v>
       </c>
       <c r="F47">
-        <v>169.6666666666666</v>
+        <v>601.55555555555543</v>
       </c>
       <c r="G47">
-        <v>169.6666666666666</v>
+        <v>494.55555555555537</v>
       </c>
       <c r="H47">
-        <v>27.833333333333329</v>
+        <v>70.499999999999972</v>
       </c>
       <c r="I47">
-        <v>4.2652508999890406</v>
+        <v>4.3583565000008093</v>
       </c>
       <c r="J47">
-        <v>2.2050300001865249E-2</v>
+        <v>0.108824499999173</v>
       </c>
       <c r="K47">
-        <v>4.2873011999909068</v>
-      </c>
-      <c r="M47">
-        <f t="shared" si="0"/>
-        <v>180.04166666666666</v>
-      </c>
-      <c r="N47">
-        <f t="shared" si="1"/>
-        <v>349.70833333333326</v>
-      </c>
-    </row>
-    <row r="48" spans="1:14" x14ac:dyDescent="0.25">
+        <v>4.4671809999999823</v>
+      </c>
+    </row>
+    <row r="48" spans="1:11">
       <c r="A48">
         <v>70000</v>
       </c>
@@ -4030,39 +3102,31 @@
         <v>700</v>
       </c>
       <c r="D48">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="E48">
         <v>47</v>
       </c>
       <c r="F48">
-        <v>360.86111111111092</v>
+        <v>303.91666666666652</v>
       </c>
       <c r="G48">
-        <v>360.86111111111092</v>
+        <v>303.91666666666652</v>
       </c>
       <c r="H48">
-        <v>50.861111111111093</v>
+        <v>46.41666666666665</v>
       </c>
       <c r="I48">
-        <v>4.2507688999903621</v>
+        <v>4.2694906999968234</v>
       </c>
       <c r="J48">
-        <v>2.2731600009137761E-2</v>
+        <v>2.4070600004051809E-2</v>
       </c>
       <c r="K48">
-        <v>4.2735004999994999</v>
-      </c>
-      <c r="M48">
-        <f t="shared" si="0"/>
-        <v>11.152777777777658</v>
-      </c>
-      <c r="N48">
-        <f t="shared" si="1"/>
-        <v>349.70833333333326</v>
-      </c>
-    </row>
-    <row r="49" spans="1:14" x14ac:dyDescent="0.25">
+        <v>4.2935613000008743</v>
+      </c>
+    </row>
+    <row r="49" spans="1:11">
       <c r="A49">
         <v>70000</v>
       </c>
@@ -4073,39 +3137,31 @@
         <v>700</v>
       </c>
       <c r="D49">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="E49">
         <v>48</v>
       </c>
       <c r="F49">
-        <v>213.6111111111112</v>
+        <v>573.75</v>
       </c>
       <c r="G49">
-        <v>213.6111111111112</v>
+        <v>548.08333333333326</v>
       </c>
       <c r="H49">
-        <v>30.000000000000011</v>
+        <v>61.583333333333307</v>
       </c>
       <c r="I49">
-        <v>4.3390712999971583</v>
+        <v>4.3390282999898773</v>
       </c>
       <c r="J49">
-        <v>2.2555200004717339E-2</v>
+        <v>8.7761600007070228E-2</v>
       </c>
       <c r="K49">
-        <v>4.3616265000018757</v>
-      </c>
-      <c r="M49">
-        <f t="shared" si="0"/>
-        <v>136.09722222222206</v>
-      </c>
-      <c r="N49">
-        <f t="shared" si="1"/>
-        <v>349.70833333333326</v>
-      </c>
-    </row>
-    <row r="50" spans="1:14" x14ac:dyDescent="0.25">
+        <v>4.4267898999969466</v>
+      </c>
+    </row>
+    <row r="50" spans="1:11">
       <c r="A50">
         <v>70000</v>
       </c>
@@ -4116,39 +3172,31 @@
         <v>700</v>
       </c>
       <c r="D50">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="E50">
         <v>49</v>
       </c>
       <c r="F50">
-        <v>249.44444444444451</v>
+        <v>171.33333333333329</v>
       </c>
       <c r="G50">
-        <v>249.44444444444451</v>
+        <v>171.33333333333329</v>
       </c>
       <c r="H50">
-        <v>37.083333333333343</v>
+        <v>28</v>
       </c>
       <c r="I50">
-        <v>4.1560023999918494</v>
+        <v>4.3137439999991329</v>
       </c>
       <c r="J50">
-        <v>2.2876899995026179E-2</v>
+        <v>2.245790000597481E-2</v>
       </c>
       <c r="K50">
-        <v>4.1788792999868747</v>
-      </c>
-      <c r="M50">
-        <f t="shared" si="0"/>
-        <v>100.26388888888874</v>
-      </c>
-      <c r="N50">
-        <f t="shared" si="1"/>
-        <v>349.70833333333326</v>
-      </c>
-    </row>
-    <row r="51" spans="1:14" x14ac:dyDescent="0.25">
+        <v>4.3362019000051077</v>
+      </c>
+    </row>
+    <row r="51" spans="1:11">
       <c r="A51">
         <v>70000</v>
       </c>
@@ -4159,40 +3207,694 @@
         <v>700</v>
       </c>
       <c r="D51">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="E51">
         <v>88</v>
       </c>
       <c r="F51">
-        <v>433.83333333333343</v>
+        <v>351.6388888888888</v>
       </c>
       <c r="G51">
-        <v>433.83333333333343</v>
+        <v>351.6388888888888</v>
       </c>
       <c r="H51">
-        <v>51.361111111111121</v>
+        <v>49.222222222222207</v>
       </c>
       <c r="I51">
-        <v>5.1256603999936488</v>
+        <v>4.8623893000039971</v>
       </c>
       <c r="J51">
-        <v>2.8741499991156161E-2</v>
+        <v>2.728169999318197E-2</v>
       </c>
       <c r="K51">
-        <v>5.1544018999848049</v>
-      </c>
-      <c r="M51">
-        <f t="shared" si="0"/>
-        <v>84.125000000000171</v>
-      </c>
-      <c r="N51">
-        <f t="shared" si="1"/>
-        <v>349.70833333333326</v>
+        <v>4.889670999997179</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{01ACB91C-B282-4EB2-B5F5-95E10D8AC8A8}">
+  <dimension ref="A1:E51"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>287.5</v>
+      </c>
+      <c r="C2" t="str">
+        <f>IF(OR(B2&lt;$E$5,B2&gt;$E$6),"Uitschieter","Normaal")</f>
+        <v>Normaal</v>
+      </c>
+      <c r="D2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2">
+        <f>_xlfn.QUARTILE.INC(B2:B51,1)</f>
+        <v>269.59027777777789</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>374.2777777777776</v>
+      </c>
+      <c r="C3" t="str">
+        <f t="shared" ref="C3:C51" si="0">IF(OR(B3&lt;$E$5,B3&gt;$E$6),"Uitschieter","Normaal")</f>
+        <v>Normaal</v>
+      </c>
+      <c r="D3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E3" s="1">
+        <f>_xlfn.QUARTILE.INC(B2:B51,3)</f>
+        <v>376.27083333333326</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <v>248.0833333333334</v>
+      </c>
+      <c r="C4" t="str">
+        <f t="shared" si="0"/>
+        <v>Normaal</v>
+      </c>
+      <c r="D4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E4" s="1">
+        <f>E3-E2</f>
+        <v>106.68055555555537</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5">
+        <v>309.27777777777783</v>
+      </c>
+      <c r="C5" t="str">
+        <f t="shared" si="0"/>
+        <v>Normaal</v>
+      </c>
+      <c r="D5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E5" s="1">
+        <f>E2-1.5*E4</f>
+        <v>109.56944444444483</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6">
+        <v>249.3888888888886</v>
+      </c>
+      <c r="C6" t="str">
+        <f t="shared" si="0"/>
+        <v>Normaal</v>
+      </c>
+      <c r="D6" t="s">
+        <v>15</v>
+      </c>
+      <c r="E6" s="1">
+        <f>E3+1.5*E4</f>
+        <v>536.29166666666629</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <v>306.00000000000023</v>
+      </c>
+      <c r="C7" t="str">
+        <f t="shared" si="0"/>
+        <v>Normaal</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8">
+        <v>533.33333333333326</v>
+      </c>
+      <c r="C8" t="str">
+        <f t="shared" si="0"/>
+        <v>Normaal</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9">
+        <v>333.33333333333343</v>
+      </c>
+      <c r="C9" t="str">
+        <f t="shared" si="0"/>
+        <v>Normaal</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10">
+        <v>228.2777777777778</v>
+      </c>
+      <c r="C10" t="str">
+        <f t="shared" si="0"/>
+        <v>Normaal</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11">
+        <v>375.08333333333331</v>
+      </c>
+      <c r="C11" t="str">
+        <f t="shared" si="0"/>
+        <v>Normaal</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12">
+        <v>168.5</v>
+      </c>
+      <c r="C12" t="str">
+        <f t="shared" si="0"/>
+        <v>Normaal</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13">
+        <v>279.69444444444429</v>
+      </c>
+      <c r="C13" t="str">
+        <f t="shared" si="0"/>
+        <v>Normaal</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14">
+        <v>282.83333333333343</v>
+      </c>
+      <c r="C14" t="str">
+        <f t="shared" si="0"/>
+        <v>Normaal</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="B15">
+        <v>267.94444444444451</v>
+      </c>
+      <c r="C15" t="str">
+        <f t="shared" si="0"/>
+        <v>Normaal</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="B16">
+        <v>254.02777777777769</v>
+      </c>
+      <c r="C16" t="str">
+        <f t="shared" si="0"/>
+        <v>Normaal</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="B17">
+        <v>612.91666666666652</v>
+      </c>
+      <c r="C17" t="str">
+        <f t="shared" si="0"/>
+        <v>Uitschieter</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18">
+        <v>17</v>
+      </c>
+      <c r="B18">
+        <v>482.66666666666669</v>
+      </c>
+      <c r="C18" t="str">
+        <f t="shared" si="0"/>
+        <v>Normaal</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19">
+        <v>18</v>
+      </c>
+      <c r="B19">
+        <v>328.58333333333343</v>
+      </c>
+      <c r="C19" t="str">
+        <f t="shared" si="0"/>
+        <v>Normaal</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20">
+        <v>19</v>
+      </c>
+      <c r="B20">
+        <v>268.47222222222229</v>
+      </c>
+      <c r="C20" t="str">
+        <f t="shared" si="0"/>
+        <v>Normaal</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21">
+        <v>20</v>
+      </c>
+      <c r="B21">
+        <v>522.5</v>
+      </c>
+      <c r="C21" t="str">
+        <f t="shared" si="0"/>
+        <v>Normaal</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3">
+      <c r="A22">
+        <v>21</v>
+      </c>
+      <c r="B22">
+        <v>333.61111111111109</v>
+      </c>
+      <c r="C22" t="str">
+        <f t="shared" si="0"/>
+        <v>Normaal</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3">
+      <c r="A23">
+        <v>22</v>
+      </c>
+      <c r="B23">
+        <v>390.6111111111112</v>
+      </c>
+      <c r="C23" t="str">
+        <f t="shared" si="0"/>
+        <v>Normaal</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3">
+      <c r="A24">
+        <v>23</v>
+      </c>
+      <c r="B24">
+        <v>192.4444444444446</v>
+      </c>
+      <c r="C24" t="str">
+        <f t="shared" si="0"/>
+        <v>Normaal</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3">
+      <c r="A25">
+        <v>24</v>
+      </c>
+      <c r="B25">
+        <v>246.7777777777776</v>
+      </c>
+      <c r="C25" t="str">
+        <f t="shared" si="0"/>
+        <v>Normaal</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3">
+      <c r="A26">
+        <v>25</v>
+      </c>
+      <c r="B26">
+        <v>461.94444444444451</v>
+      </c>
+      <c r="C26" t="str">
+        <f t="shared" si="0"/>
+        <v>Normaal</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3">
+      <c r="A27">
+        <v>26</v>
+      </c>
+      <c r="B27">
+        <v>378</v>
+      </c>
+      <c r="C27" t="str">
+        <f t="shared" si="0"/>
+        <v>Normaal</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3">
+      <c r="A28">
+        <v>27</v>
+      </c>
+      <c r="B28">
+        <v>334.94444444444417</v>
+      </c>
+      <c r="C28" t="str">
+        <f t="shared" si="0"/>
+        <v>Normaal</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3">
+      <c r="A29">
+        <v>28</v>
+      </c>
+      <c r="B29">
+        <v>315.8333333333336</v>
+      </c>
+      <c r="C29" t="str">
+        <f t="shared" si="0"/>
+        <v>Normaal</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3">
+      <c r="A30">
+        <v>29</v>
+      </c>
+      <c r="B30">
+        <v>358.02777777777749</v>
+      </c>
+      <c r="C30" t="str">
+        <f t="shared" si="0"/>
+        <v>Normaal</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3">
+      <c r="A31">
+        <v>30</v>
+      </c>
+      <c r="B31">
+        <v>252.61111111111109</v>
+      </c>
+      <c r="C31" t="str">
+        <f t="shared" si="0"/>
+        <v>Normaal</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3">
+      <c r="A32">
+        <v>31</v>
+      </c>
+      <c r="B32">
+        <v>295.16666666666691</v>
+      </c>
+      <c r="C32" t="str">
+        <f t="shared" si="0"/>
+        <v>Normaal</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3">
+      <c r="A33">
+        <v>32</v>
+      </c>
+      <c r="B33">
+        <v>290.58333333333331</v>
+      </c>
+      <c r="C33" t="str">
+        <f t="shared" si="0"/>
+        <v>Normaal</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3">
+      <c r="A34">
+        <v>33</v>
+      </c>
+      <c r="B34">
+        <v>272.94444444444463</v>
+      </c>
+      <c r="C34" t="str">
+        <f t="shared" si="0"/>
+        <v>Normaal</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3">
+      <c r="A35">
+        <v>34</v>
+      </c>
+      <c r="B35">
+        <v>376.66666666666657</v>
+      </c>
+      <c r="C35" t="str">
+        <f t="shared" si="0"/>
+        <v>Normaal</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3">
+      <c r="A36">
+        <v>35</v>
+      </c>
+      <c r="B36">
+        <v>178.7777777777778</v>
+      </c>
+      <c r="C36" t="str">
+        <f t="shared" si="0"/>
+        <v>Normaal</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3">
+      <c r="A37">
+        <v>36</v>
+      </c>
+      <c r="B37">
+        <v>308.55555555555537</v>
+      </c>
+      <c r="C37" t="str">
+        <f t="shared" si="0"/>
+        <v>Normaal</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3">
+      <c r="A38">
+        <v>37</v>
+      </c>
+      <c r="B38">
+        <v>313.27777777777783</v>
+      </c>
+      <c r="C38" t="str">
+        <f t="shared" si="0"/>
+        <v>Normaal</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3">
+      <c r="A39">
+        <v>38</v>
+      </c>
+      <c r="B39">
+        <v>395.88888888888869</v>
+      </c>
+      <c r="C39" t="str">
+        <f t="shared" si="0"/>
+        <v>Normaal</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3">
+      <c r="A40">
+        <v>39</v>
+      </c>
+      <c r="B40">
+        <v>314.77777777777783</v>
+      </c>
+      <c r="C40" t="str">
+        <f t="shared" si="0"/>
+        <v>Normaal</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3">
+      <c r="A41">
+        <v>40</v>
+      </c>
+      <c r="B41">
+        <v>444.77777777777783</v>
+      </c>
+      <c r="C41" t="str">
+        <f t="shared" si="0"/>
+        <v>Normaal</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3">
+      <c r="A42">
+        <v>41</v>
+      </c>
+      <c r="B42">
+        <v>623.00000000000011</v>
+      </c>
+      <c r="C42" t="str">
+        <f t="shared" si="0"/>
+        <v>Uitschieter</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3">
+      <c r="A43">
+        <v>42</v>
+      </c>
+      <c r="B43">
+        <v>323.5</v>
+      </c>
+      <c r="C43" t="str">
+        <f t="shared" si="0"/>
+        <v>Normaal</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3">
+      <c r="A44">
+        <v>43</v>
+      </c>
+      <c r="B44">
+        <v>208.16666666666671</v>
+      </c>
+      <c r="C44" t="str">
+        <f t="shared" si="0"/>
+        <v>Normaal</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3">
+      <c r="A45">
+        <v>44</v>
+      </c>
+      <c r="B45">
+        <v>328.33333333333331</v>
+      </c>
+      <c r="C45" t="str">
+        <f t="shared" si="0"/>
+        <v>Normaal</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3">
+      <c r="A46">
+        <v>45</v>
+      </c>
+      <c r="B46">
+        <v>292.27777777777771</v>
+      </c>
+      <c r="C46" t="str">
+        <f t="shared" si="0"/>
+        <v>Normaal</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3">
+      <c r="A47">
+        <v>46</v>
+      </c>
+      <c r="B47">
+        <v>494.55555555555537</v>
+      </c>
+      <c r="C47" t="str">
+        <f t="shared" si="0"/>
+        <v>Normaal</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3">
+      <c r="A48">
+        <v>47</v>
+      </c>
+      <c r="B48">
+        <v>303.91666666666652</v>
+      </c>
+      <c r="C48" t="str">
+        <f t="shared" si="0"/>
+        <v>Normaal</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3">
+      <c r="A49">
+        <v>48</v>
+      </c>
+      <c r="B49">
+        <v>548.08333333333326</v>
+      </c>
+      <c r="C49" t="str">
+        <f t="shared" si="0"/>
+        <v>Uitschieter</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3">
+      <c r="A50">
+        <v>49</v>
+      </c>
+      <c r="B50">
+        <v>171.33333333333329</v>
+      </c>
+      <c r="C50" t="str">
+        <f t="shared" si="0"/>
+        <v>Normaal</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3">
+      <c r="A51">
+        <v>88</v>
+      </c>
+      <c r="B51">
+        <v>351.6388888888888</v>
+      </c>
+      <c r="C51" t="str">
+        <f t="shared" si="0"/>
+        <v>Normaal</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>